--- a/research/traditional_assets/database/data/austria/austria_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_business_consumer_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09217471871865685</v>
+        <v>0.09198769939373207</v>
       </c>
       <c r="C2">
-        <v>2425.25249246398</v>
+        <v>2407.788923114359</v>
       </c>
       <c r="D2">
-        <v>2131.25249246398</v>
+        <v>2139.009923114359</v>
       </c>
       <c r="E2">
-        <v>-475.3</v>
+        <v>-450.079</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25.221</v>
       </c>
       <c r="G2">
         <v>294</v>
@@ -1457,28 +1457,28 @@
         <v>151.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2686163</v>
       </c>
       <c r="N2">
-        <v>151.6</v>
+        <v>150.3313837</v>
       </c>
       <c r="O2">
-        <v>36.384</v>
+        <v>36.079532088</v>
       </c>
       <c r="P2">
-        <v>115.216</v>
+        <v>114.251851612</v>
       </c>
       <c r="Q2">
-        <v>196.316</v>
+        <v>195.351851612</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09217471871865685</v>
+        <v>0.09253072666033542</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9608329250785119</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.5002775859021</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09198769939373207</v>
+        <v>0.09180068006880727</v>
       </c>
       <c r="C3">
-        <v>2407.788923114359</v>
+        <v>2390.38203176826</v>
       </c>
       <c r="D3">
-        <v>2139.009923114359</v>
+        <v>2146.82403176826</v>
       </c>
       <c r="E3">
-        <v>-450.079</v>
+        <v>-424.858</v>
       </c>
       <c r="F3">
-        <v>25.221</v>
+        <v>50.442</v>
       </c>
       <c r="G3">
         <v>294</v>
@@ -1539,28 +1539,28 @@
         <v>151.6</v>
       </c>
       <c r="M3">
-        <v>1.2686163</v>
+        <v>2.5372326</v>
       </c>
       <c r="N3">
-        <v>150.3313837</v>
+        <v>149.0627674</v>
       </c>
       <c r="O3">
-        <v>36.079532088</v>
+        <v>35.77506417599999</v>
       </c>
       <c r="P3">
-        <v>114.251851612</v>
+        <v>113.287703224</v>
       </c>
       <c r="Q3">
-        <v>195.351851612</v>
+        <v>194.387703224</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09253072666033542</v>
+        <v>0.09289400007021151</v>
       </c>
       <c r="T3">
-        <v>0.9608329250785119</v>
+        <v>0.9683022087374532</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.5002775859021</v>
+        <v>59.75013879295103</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09180068006880727</v>
+        <v>0.09161366074388251</v>
       </c>
       <c r="C4">
-        <v>2390.38203176826</v>
+        <v>2373.0324418617</v>
       </c>
       <c r="D4">
-        <v>2146.82403176826</v>
+        <v>2154.6954418617</v>
       </c>
       <c r="E4">
-        <v>-424.858</v>
+        <v>-399.637</v>
       </c>
       <c r="F4">
-        <v>50.442</v>
+        <v>75.663</v>
       </c>
       <c r="G4">
         <v>294</v>
@@ -1621,28 +1621,28 @@
         <v>151.6</v>
       </c>
       <c r="M4">
-        <v>2.5372326</v>
+        <v>3.8058489</v>
       </c>
       <c r="N4">
-        <v>149.0627674</v>
+        <v>147.7941511</v>
       </c>
       <c r="O4">
-        <v>35.77506417599999</v>
+        <v>35.47059626399999</v>
       </c>
       <c r="P4">
-        <v>113.287703224</v>
+        <v>112.323554836</v>
       </c>
       <c r="Q4">
-        <v>194.387703224</v>
+        <v>193.423554836</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09289400007021151</v>
+        <v>0.09326476365348713</v>
       </c>
       <c r="T4">
-        <v>0.9683022087374532</v>
+        <v>0.9759254982450326</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.75013879295103</v>
+        <v>39.83342586196736</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09161366074388251</v>
+        <v>0.09142664141895773</v>
       </c>
       <c r="C5">
-        <v>2373.0324418617</v>
+        <v>2355.740786007752</v>
       </c>
       <c r="D5">
-        <v>2154.6954418617</v>
+        <v>2162.624786007752</v>
       </c>
       <c r="E5">
-        <v>-399.637</v>
+        <v>-374.416</v>
       </c>
       <c r="F5">
-        <v>75.663</v>
+        <v>100.884</v>
       </c>
       <c r="G5">
         <v>294</v>
@@ -1703,28 +1703,28 @@
         <v>151.6</v>
       </c>
       <c r="M5">
-        <v>3.8058489</v>
+        <v>5.0744652</v>
       </c>
       <c r="N5">
-        <v>147.7941511</v>
+        <v>146.5255348</v>
       </c>
       <c r="O5">
-        <v>35.47059626399999</v>
+        <v>35.166128352</v>
       </c>
       <c r="P5">
-        <v>112.323554836</v>
+        <v>111.359406448</v>
       </c>
       <c r="Q5">
-        <v>193.423554836</v>
+        <v>192.459406448</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09326476365348713</v>
+        <v>0.09364325147808097</v>
       </c>
       <c r="T5">
-        <v>0.9759254982450326</v>
+        <v>0.9837076062840198</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.83342586196736</v>
+        <v>29.87506939647552</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09142664141895773</v>
+        <v>0.09123962209403294</v>
       </c>
       <c r="C6">
-        <v>2355.740786007752</v>
+        <v>2338.507706166025</v>
       </c>
       <c r="D6">
-        <v>2162.624786007752</v>
+        <v>2170.612706166025</v>
       </c>
       <c r="E6">
-        <v>-374.416</v>
+        <v>-349.195</v>
       </c>
       <c r="F6">
-        <v>100.884</v>
+        <v>126.105</v>
       </c>
       <c r="G6">
         <v>294</v>
@@ -1785,28 +1785,28 @@
         <v>151.6</v>
       </c>
       <c r="M6">
-        <v>5.0744652</v>
+        <v>6.3430815</v>
       </c>
       <c r="N6">
-        <v>146.5255348</v>
+        <v>145.2569185</v>
       </c>
       <c r="O6">
-        <v>35.166128352</v>
+        <v>34.86166043999999</v>
       </c>
       <c r="P6">
-        <v>111.359406448</v>
+        <v>110.39525806</v>
       </c>
       <c r="Q6">
-        <v>192.459406448</v>
+        <v>191.49525806</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09364325147808097</v>
+        <v>0.09402970746740311</v>
       </c>
       <c r="T6">
-        <v>0.9837076062840198</v>
+        <v>0.9916535481764593</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.87506939647552</v>
+        <v>23.90005551718041</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09123962209403294</v>
+        <v>0.09105260276910818</v>
       </c>
       <c r="C7">
-        <v>2338.507706166025</v>
+        <v>2321.333853815914</v>
       </c>
       <c r="D7">
-        <v>2170.612706166025</v>
+        <v>2178.659853815914</v>
       </c>
       <c r="E7">
-        <v>-349.195</v>
+        <v>-323.974</v>
       </c>
       <c r="F7">
-        <v>126.105</v>
+        <v>151.326</v>
       </c>
       <c r="G7">
         <v>294</v>
@@ -1867,28 +1867,28 @@
         <v>151.6</v>
       </c>
       <c r="M7">
-        <v>6.3430815</v>
+        <v>7.611697799999999</v>
       </c>
       <c r="N7">
-        <v>145.2569185</v>
+        <v>143.9883022</v>
       </c>
       <c r="O7">
-        <v>34.86166043999999</v>
+        <v>34.55719252799999</v>
       </c>
       <c r="P7">
-        <v>110.39525806</v>
+        <v>109.431109672</v>
       </c>
       <c r="Q7">
-        <v>191.49525806</v>
+        <v>190.531109672</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09402970746740311</v>
+        <v>0.09442438592458316</v>
       </c>
       <c r="T7">
-        <v>0.9916535481764593</v>
+        <v>0.9997685526623551</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.90005551718041</v>
+        <v>19.91671293098368</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09105260276910818</v>
+        <v>0.09086558344418341</v>
       </c>
       <c r="C8">
-        <v>2321.333853815914</v>
+        <v>2304.219890133726</v>
       </c>
       <c r="D8">
-        <v>2178.659853815914</v>
+        <v>2186.766890133726</v>
       </c>
       <c r="E8">
-        <v>-323.974</v>
+        <v>-298.753</v>
       </c>
       <c r="F8">
-        <v>151.326</v>
+        <v>176.547</v>
       </c>
       <c r="G8">
         <v>294</v>
@@ -1949,28 +1949,28 @@
         <v>151.6</v>
       </c>
       <c r="M8">
-        <v>7.611697799999999</v>
+        <v>8.880314099999998</v>
       </c>
       <c r="N8">
-        <v>143.9883022</v>
+        <v>142.7196859</v>
       </c>
       <c r="O8">
-        <v>34.55719252799999</v>
+        <v>34.252724616</v>
       </c>
       <c r="P8">
-        <v>109.431109672</v>
+        <v>108.466961284</v>
       </c>
       <c r="Q8">
-        <v>190.531109672</v>
+        <v>189.566961284</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09442438592458316</v>
+        <v>0.09482755209051978</v>
       </c>
       <c r="T8">
-        <v>0.9997685526623551</v>
+        <v>1.008058073373754</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.91671293098368</v>
+        <v>17.07146822655744</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0908655834441834</v>
+        <v>0.09067856411925862</v>
       </c>
       <c r="C9">
-        <v>2304.219890133726</v>
+        <v>2287.166486173772</v>
       </c>
       <c r="D9">
-        <v>2186.766890133727</v>
+        <v>2194.934486173772</v>
       </c>
       <c r="E9">
-        <v>-298.753</v>
+        <v>-273.532</v>
       </c>
       <c r="F9">
-        <v>176.547</v>
+        <v>201.768</v>
       </c>
       <c r="G9">
         <v>294</v>
@@ -2031,28 +2031,28 @@
         <v>151.6</v>
       </c>
       <c r="M9">
-        <v>8.8803141</v>
+        <v>10.1489304</v>
       </c>
       <c r="N9">
-        <v>142.7196859</v>
+        <v>141.4510696</v>
       </c>
       <c r="O9">
-        <v>34.252724616</v>
+        <v>33.94825670399999</v>
       </c>
       <c r="P9">
-        <v>108.466961284</v>
+        <v>107.502812896</v>
       </c>
       <c r="Q9">
-        <v>189.566961284</v>
+        <v>188.602812896</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09482755209051978</v>
+        <v>0.09523948273832458</v>
       </c>
       <c r="T9">
-        <v>1.008058073373754</v>
+        <v>1.01652780105714</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.07146822655744</v>
+        <v>14.93753469823776</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09067856411925862</v>
+        <v>0.09049154479433386</v>
       </c>
       <c r="C10">
-        <v>2287.166486173772</v>
+        <v>2270.174323053519</v>
       </c>
       <c r="D10">
-        <v>2194.934486173772</v>
+        <v>2203.163323053519</v>
       </c>
       <c r="E10">
-        <v>-273.532</v>
+        <v>-248.311</v>
       </c>
       <c r="F10">
-        <v>201.768</v>
+        <v>226.989</v>
       </c>
       <c r="G10">
         <v>294</v>
@@ -2113,28 +2113,28 @@
         <v>151.6</v>
       </c>
       <c r="M10">
-        <v>10.1489304</v>
+        <v>11.4175467</v>
       </c>
       <c r="N10">
-        <v>141.4510696</v>
+        <v>140.1824533</v>
       </c>
       <c r="O10">
-        <v>33.94825670399999</v>
+        <v>33.643788792</v>
       </c>
       <c r="P10">
-        <v>107.502812896</v>
+        <v>106.538664508</v>
       </c>
       <c r="Q10">
-        <v>188.602812896</v>
+        <v>187.638664508</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09523948273832458</v>
+        <v>0.09566046680696028</v>
       </c>
       <c r="T10">
-        <v>1.01652780105714</v>
+        <v>1.025183676601699</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.93753469823776</v>
+        <v>13.27780862065578</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09049154479433386</v>
+        <v>0.09041852546940908</v>
       </c>
       <c r="C11">
-        <v>2270.174323053519</v>
+        <v>2248.182940474876</v>
       </c>
       <c r="D11">
-        <v>2203.163323053519</v>
+        <v>2206.392940474876</v>
       </c>
       <c r="E11">
-        <v>-248.311</v>
+        <v>-223.09</v>
       </c>
       <c r="F11">
-        <v>226.989</v>
+        <v>252.21</v>
       </c>
       <c r="G11">
         <v>294</v>
@@ -2195,45 +2195,45 @@
         <v>151.6</v>
       </c>
       <c r="M11">
-        <v>11.4175467</v>
+        <v>13.064478</v>
       </c>
       <c r="N11">
-        <v>140.1824533</v>
+        <v>138.535522</v>
       </c>
       <c r="O11">
-        <v>33.643788792</v>
+        <v>33.24852528</v>
       </c>
       <c r="P11">
-        <v>106.538664508</v>
+        <v>105.28699672</v>
       </c>
       <c r="Q11">
-        <v>187.638664508</v>
+        <v>186.38699672</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09566046680696028</v>
+        <v>0.0960908060771212</v>
       </c>
       <c r="T11">
-        <v>1.025183676601699</v>
+        <v>1.034031904936137</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.27780862065578</v>
+        <v>11.60398448372755</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09041852546940908</v>
+        <v>0.09024290614448428</v>
       </c>
       <c r="C12">
-        <v>2248.182940474876</v>
+        <v>2230.768426919468</v>
       </c>
       <c r="D12">
-        <v>2206.392940474876</v>
+        <v>2214.199426919468</v>
       </c>
       <c r="E12">
-        <v>-223.09</v>
+        <v>-197.869</v>
       </c>
       <c r="F12">
-        <v>252.21</v>
+        <v>277.431</v>
       </c>
       <c r="G12">
         <v>294</v>
@@ -2277,28 +2277,28 @@
         <v>151.6</v>
       </c>
       <c r="M12">
-        <v>13.064478</v>
+        <v>14.3709258</v>
       </c>
       <c r="N12">
-        <v>138.535522</v>
+        <v>137.2290742</v>
       </c>
       <c r="O12">
-        <v>33.24852528</v>
+        <v>32.93497780799999</v>
       </c>
       <c r="P12">
-        <v>105.28699672</v>
+        <v>104.294096392</v>
       </c>
       <c r="Q12">
-        <v>186.38699672</v>
+        <v>185.394096392</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0960908060771212</v>
+        <v>0.09653081589267898</v>
       </c>
       <c r="T12">
-        <v>1.034031904936137</v>
+        <v>1.04307896986236</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.60398448372755</v>
+        <v>10.54907680338869</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09024290614448428</v>
+        <v>0.09022232681955951</v>
       </c>
       <c r="C13">
-        <v>2230.768426919468</v>
+        <v>2206.465819575675</v>
       </c>
       <c r="D13">
-        <v>2214.199426919468</v>
+        <v>2215.117819575675</v>
       </c>
       <c r="E13">
-        <v>-197.869</v>
+        <v>-172.648</v>
       </c>
       <c r="F13">
-        <v>277.431</v>
+        <v>302.652</v>
       </c>
       <c r="G13">
         <v>294</v>
@@ -2359,45 +2359,45 @@
         <v>151.6</v>
       </c>
       <c r="M13">
-        <v>14.3709258</v>
+        <v>16.191882</v>
       </c>
       <c r="N13">
-        <v>137.2290742</v>
+        <v>135.408118</v>
       </c>
       <c r="O13">
-        <v>32.93497780799999</v>
+        <v>32.49794832</v>
       </c>
       <c r="P13">
-        <v>104.294096392</v>
+        <v>102.91016968</v>
       </c>
       <c r="Q13">
-        <v>185.394096392</v>
+        <v>184.01016968</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09653081589267898</v>
+        <v>0.09698082593131763</v>
       </c>
       <c r="T13">
-        <v>1.04307896986236</v>
+        <v>1.052331649900543</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.54907680338869</v>
+        <v>9.362716452602607</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09022232681955951</v>
+        <v>0.09005962749463473</v>
       </c>
       <c r="C14">
-        <v>2206.465819575675</v>
+        <v>2188.532504684323</v>
       </c>
       <c r="D14">
-        <v>2215.117819575675</v>
+        <v>2222.405504684323</v>
       </c>
       <c r="E14">
-        <v>-172.648</v>
+        <v>-147.427</v>
       </c>
       <c r="F14">
-        <v>302.652</v>
+        <v>327.873</v>
       </c>
       <c r="G14">
         <v>294</v>
@@ -2441,28 +2441,28 @@
         <v>151.6</v>
       </c>
       <c r="M14">
-        <v>16.191882</v>
+        <v>17.5412055</v>
       </c>
       <c r="N14">
-        <v>135.408118</v>
+        <v>134.0587945</v>
       </c>
       <c r="O14">
-        <v>32.49794832</v>
+        <v>32.17411068</v>
       </c>
       <c r="P14">
-        <v>102.91016968</v>
+        <v>101.88468382</v>
       </c>
       <c r="Q14">
-        <v>184.01016968</v>
+        <v>182.98468382</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09698082593131763</v>
+        <v>0.09744118102831578</v>
       </c>
       <c r="T14">
-        <v>1.052331649900543</v>
+        <v>1.06179703522696</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.362716452602607</v>
+        <v>8.642507494710099</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09005962749463473</v>
+        <v>0.08989692816970996</v>
       </c>
       <c r="C15">
-        <v>2188.532504684323</v>
+        <v>2170.647300699161</v>
       </c>
       <c r="D15">
-        <v>2222.405504684323</v>
+        <v>2229.741300699161</v>
       </c>
       <c r="E15">
-        <v>-147.427</v>
+        <v>-122.206</v>
       </c>
       <c r="F15">
-        <v>327.873</v>
+        <v>353.094</v>
       </c>
       <c r="G15">
         <v>294</v>
@@ -2523,28 +2523,28 @@
         <v>151.6</v>
       </c>
       <c r="M15">
-        <v>17.5412055</v>
+        <v>18.890529</v>
       </c>
       <c r="N15">
-        <v>134.0587945</v>
+        <v>132.709471</v>
       </c>
       <c r="O15">
-        <v>32.17411068</v>
+        <v>31.85027304</v>
       </c>
       <c r="P15">
-        <v>101.88468382</v>
+        <v>100.85919796</v>
       </c>
       <c r="Q15">
-        <v>182.98468382</v>
+        <v>181.95919796</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09744118102831578</v>
+        <v>0.09791224205780227</v>
       </c>
       <c r="T15">
-        <v>1.06179703522696</v>
+        <v>1.071482545793527</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.642507494710099</v>
+        <v>8.025185530802235</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08989692816970996</v>
+        <v>0.0898254288447852</v>
       </c>
       <c r="C16">
-        <v>2170.647300699161</v>
+        <v>2148.665405836995</v>
       </c>
       <c r="D16">
-        <v>2229.741300699161</v>
+        <v>2232.980405836995</v>
       </c>
       <c r="E16">
-        <v>-122.206</v>
+        <v>-96.98499999999996</v>
       </c>
       <c r="F16">
-        <v>353.094</v>
+        <v>378.3150000000001</v>
       </c>
       <c r="G16">
         <v>294</v>
@@ -2605,45 +2605,45 @@
         <v>151.6</v>
       </c>
       <c r="M16">
-        <v>18.890529</v>
+        <v>20.5425045</v>
       </c>
       <c r="N16">
-        <v>132.709471</v>
+        <v>131.0574955</v>
       </c>
       <c r="O16">
-        <v>31.85027304</v>
+        <v>31.45379892</v>
       </c>
       <c r="P16">
-        <v>100.85919796</v>
+        <v>99.60369657999999</v>
       </c>
       <c r="Q16">
-        <v>181.95919796</v>
+        <v>180.70369658</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09791224205780227</v>
+        <v>0.09839438687621788</v>
       </c>
       <c r="T16">
-        <v>1.071482545793527</v>
+        <v>1.081395950726365</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.025185530802235</v>
+        <v>7.379820702972219</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0898254288447852</v>
+        <v>0.08966880951986042</v>
       </c>
       <c r="C17">
-        <v>2148.665405836995</v>
+        <v>2130.572658052325</v>
       </c>
       <c r="D17">
-        <v>2232.980405836995</v>
+        <v>2240.108658052325</v>
       </c>
       <c r="E17">
-        <v>-96.98500000000001</v>
+        <v>-71.76400000000001</v>
       </c>
       <c r="F17">
-        <v>378.315</v>
+        <v>403.536</v>
       </c>
       <c r="G17">
         <v>294</v>
@@ -2687,28 +2687,28 @@
         <v>151.6</v>
       </c>
       <c r="M17">
-        <v>20.5425045</v>
+        <v>21.9120048</v>
       </c>
       <c r="N17">
-        <v>131.0574955</v>
+        <v>129.6879952</v>
       </c>
       <c r="O17">
-        <v>31.45379892</v>
+        <v>31.125118848</v>
       </c>
       <c r="P17">
-        <v>99.60369657999999</v>
+        <v>98.56287635199999</v>
       </c>
       <c r="Q17">
-        <v>180.70369658</v>
+        <v>179.662876352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09839438687621788</v>
+        <v>0.09888801133316716</v>
       </c>
       <c r="T17">
-        <v>1.081395950726365</v>
+        <v>1.091545389109986</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.37982070297222</v>
+        <v>6.918581909036456</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08966880951986042</v>
+        <v>0.08951219019493564</v>
       </c>
       <c r="C18">
-        <v>2130.572658052325</v>
+        <v>2112.525566471335</v>
       </c>
       <c r="D18">
-        <v>2240.108658052325</v>
+        <v>2247.282566471335</v>
       </c>
       <c r="E18">
-        <v>-71.76400000000001</v>
+        <v>-46.54300000000001</v>
       </c>
       <c r="F18">
-        <v>403.536</v>
+        <v>428.757</v>
       </c>
       <c r="G18">
         <v>294</v>
@@ -2769,28 +2769,28 @@
         <v>151.6</v>
       </c>
       <c r="M18">
-        <v>21.9120048</v>
+        <v>23.2815051</v>
       </c>
       <c r="N18">
-        <v>129.6879952</v>
+        <v>128.3184949</v>
       </c>
       <c r="O18">
-        <v>31.125118848</v>
+        <v>30.796438776</v>
       </c>
       <c r="P18">
-        <v>98.56287635199999</v>
+        <v>97.52205612399999</v>
       </c>
       <c r="Q18">
-        <v>179.662876352</v>
+        <v>178.622056124</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09888801133316716</v>
+        <v>0.09939353035534415</v>
       </c>
       <c r="T18">
-        <v>1.091545389109986</v>
+        <v>1.101939392273934</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.918581909036456</v>
+        <v>6.511606502622547</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08951219019493564</v>
+        <v>0.08935557087001086</v>
       </c>
       <c r="C19">
-        <v>2112.525566471335</v>
+        <v>2094.524571142835</v>
       </c>
       <c r="D19">
-        <v>2247.282566471335</v>
+        <v>2254.502571142835</v>
       </c>
       <c r="E19">
-        <v>-46.54300000000001</v>
+        <v>-21.322</v>
       </c>
       <c r="F19">
-        <v>428.757</v>
+        <v>453.978</v>
       </c>
       <c r="G19">
         <v>294</v>
@@ -2851,28 +2851,28 @@
         <v>151.6</v>
       </c>
       <c r="M19">
-        <v>23.2815051</v>
+        <v>24.6510054</v>
       </c>
       <c r="N19">
-        <v>128.3184949</v>
+        <v>126.9489946</v>
       </c>
       <c r="O19">
-        <v>30.796438776</v>
+        <v>30.467758704</v>
       </c>
       <c r="P19">
-        <v>97.52205612399999</v>
+        <v>96.48123589599999</v>
       </c>
       <c r="Q19">
-        <v>178.622056124</v>
+        <v>177.581235896</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09939353035534415</v>
+        <v>0.09991137910976935</v>
       </c>
       <c r="T19">
-        <v>1.101939392273934</v>
+        <v>1.112586907710174</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.511606502622547</v>
+        <v>6.149850585810182</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08935557087001085</v>
+        <v>0.08934335154508609</v>
       </c>
       <c r="C20">
-        <v>2094.524571142835</v>
+        <v>2069.868822051866</v>
       </c>
       <c r="D20">
-        <v>2254.502571142835</v>
+        <v>2255.067822051866</v>
       </c>
       <c r="E20">
-        <v>-21.32200000000006</v>
+        <v>3.899000000000001</v>
       </c>
       <c r="F20">
-        <v>453.978</v>
+        <v>479.199</v>
       </c>
       <c r="G20">
         <v>294</v>
@@ -2933,45 +2933,45 @@
         <v>151.6</v>
       </c>
       <c r="M20">
-        <v>24.6510054</v>
+        <v>26.4997047</v>
       </c>
       <c r="N20">
-        <v>126.9489946</v>
+        <v>125.1002953</v>
       </c>
       <c r="O20">
-        <v>30.467758704</v>
+        <v>30.024070872</v>
       </c>
       <c r="P20">
-        <v>96.48123589599999</v>
+        <v>95.076224428</v>
       </c>
       <c r="Q20">
-        <v>177.581235896</v>
+        <v>176.176224428</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09991137910976933</v>
+        <v>0.1004420142531927</v>
       </c>
       <c r="T20">
-        <v>1.112586907710174</v>
+        <v>1.123497324762123</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.149850585810183</v>
+        <v>5.720818466328041</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08934335154508609</v>
+        <v>0.08919433222016131</v>
       </c>
       <c r="C21">
-        <v>2069.868822051866</v>
+        <v>2051.56414828263</v>
       </c>
       <c r="D21">
-        <v>2255.067822051866</v>
+        <v>2261.98414828263</v>
       </c>
       <c r="E21">
-        <v>3.899000000000001</v>
+        <v>29.12</v>
       </c>
       <c r="F21">
-        <v>479.199</v>
+        <v>504.42</v>
       </c>
       <c r="G21">
         <v>294</v>
@@ -3015,28 +3015,28 @@
         <v>151.6</v>
       </c>
       <c r="M21">
-        <v>26.4997047</v>
+        <v>27.894426</v>
       </c>
       <c r="N21">
-        <v>125.1002953</v>
+        <v>123.705574</v>
       </c>
       <c r="O21">
-        <v>30.024070872</v>
+        <v>29.68933775999999</v>
       </c>
       <c r="P21">
-        <v>95.076224428</v>
+        <v>94.01623623999998</v>
       </c>
       <c r="Q21">
-        <v>176.176224428</v>
+        <v>175.11623624</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1004420142531927</v>
+        <v>0.1009859152752016</v>
       </c>
       <c r="T21">
-        <v>1.123497324762123</v>
+        <v>1.134680502240372</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.720818466328041</v>
+        <v>5.434777543011639</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08919433222016131</v>
+        <v>0.08904531289523654</v>
       </c>
       <c r="C22">
-        <v>2051.56414828263</v>
+        <v>2033.302029980513</v>
       </c>
       <c r="D22">
-        <v>2261.98414828263</v>
+        <v>2268.943029980514</v>
       </c>
       <c r="E22">
-        <v>29.12</v>
+        <v>54.34100000000007</v>
       </c>
       <c r="F22">
-        <v>504.42</v>
+        <v>529.6410000000001</v>
       </c>
       <c r="G22">
         <v>294</v>
@@ -3097,28 +3097,28 @@
         <v>151.6</v>
       </c>
       <c r="M22">
-        <v>27.894426</v>
+        <v>29.28914730000001</v>
       </c>
       <c r="N22">
-        <v>123.705574</v>
+        <v>122.3108527</v>
       </c>
       <c r="O22">
-        <v>29.68933775999999</v>
+        <v>29.354604648</v>
       </c>
       <c r="P22">
-        <v>94.01623623999998</v>
+        <v>92.95624805199999</v>
       </c>
       <c r="Q22">
-        <v>175.11623624</v>
+        <v>174.056248052</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1009859152752016</v>
+        <v>0.1015435859433374</v>
       </c>
       <c r="T22">
-        <v>1.134680502240372</v>
+        <v>1.146146798135791</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.434777543011639</v>
+        <v>5.175978612392036</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08904531289523654</v>
+        <v>0.08889629357031176</v>
       </c>
       <c r="C23">
-        <v>2033.302029980513</v>
+        <v>2015.082861116883</v>
       </c>
       <c r="D23">
-        <v>2268.943029980514</v>
+        <v>2275.944861116883</v>
       </c>
       <c r="E23">
-        <v>54.34099999999995</v>
+        <v>79.56199999999995</v>
       </c>
       <c r="F23">
-        <v>529.641</v>
+        <v>554.862</v>
       </c>
       <c r="G23">
         <v>294</v>
@@ -3179,28 +3179,28 @@
         <v>151.6</v>
       </c>
       <c r="M23">
-        <v>29.2891473</v>
+        <v>30.6838686</v>
       </c>
       <c r="N23">
-        <v>122.3108527</v>
+        <v>120.9161314</v>
       </c>
       <c r="O23">
-        <v>29.354604648</v>
+        <v>29.019871536</v>
       </c>
       <c r="P23">
-        <v>92.95624805200001</v>
+        <v>91.896259864</v>
       </c>
       <c r="Q23">
-        <v>174.056248052</v>
+        <v>172.996259864</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1015435859433374</v>
+        <v>0.102115555859374</v>
       </c>
       <c r="T23">
-        <v>1.146146798135791</v>
+        <v>1.157907101618272</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.175978612392038</v>
+        <v>4.940706857283309</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08889629357031176</v>
+        <v>0.08874727424538698</v>
       </c>
       <c r="C24">
-        <v>2015.082861116883</v>
+        <v>1996.907040541252</v>
       </c>
       <c r="D24">
-        <v>2275.944861116883</v>
+        <v>2282.990040541252</v>
       </c>
       <c r="E24">
-        <v>79.56199999999995</v>
+        <v>104.783</v>
       </c>
       <c r="F24">
-        <v>554.862</v>
+        <v>580.083</v>
       </c>
       <c r="G24">
         <v>294</v>
@@ -3261,28 +3261,28 @@
         <v>151.6</v>
       </c>
       <c r="M24">
-        <v>30.6838686</v>
+        <v>32.0785899</v>
       </c>
       <c r="N24">
-        <v>120.9161314</v>
+        <v>119.5214101</v>
       </c>
       <c r="O24">
-        <v>29.019871536</v>
+        <v>28.685138424</v>
       </c>
       <c r="P24">
-        <v>91.896259864</v>
+        <v>90.836271676</v>
       </c>
       <c r="Q24">
-        <v>172.996259864</v>
+        <v>171.936271676</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.102115555859374</v>
+        <v>0.1027023821368662</v>
       </c>
       <c r="T24">
-        <v>1.157907101618272</v>
+        <v>1.16997286752887</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.940706857283309</v>
+        <v>4.725893515662296</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08874727424538698</v>
+        <v>0.08859825492046221</v>
       </c>
       <c r="C25">
-        <v>1996.907040541252</v>
+        <v>1978.774972057016</v>
       </c>
       <c r="D25">
-        <v>2282.990040541252</v>
+        <v>2290.078972057016</v>
       </c>
       <c r="E25">
-        <v>104.783</v>
+        <v>130.004</v>
       </c>
       <c r="F25">
-        <v>580.083</v>
+        <v>605.304</v>
       </c>
       <c r="G25">
         <v>294</v>
@@ -3343,28 +3343,28 @@
         <v>151.6</v>
       </c>
       <c r="M25">
-        <v>32.0785899</v>
+        <v>33.4733112</v>
       </c>
       <c r="N25">
-        <v>119.5214101</v>
+        <v>118.1266888</v>
       </c>
       <c r="O25">
-        <v>28.685138424</v>
+        <v>28.350405312</v>
       </c>
       <c r="P25">
-        <v>90.836271676</v>
+        <v>89.77628348799999</v>
       </c>
       <c r="Q25">
-        <v>171.936271676</v>
+        <v>170.876283488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1027023821368662</v>
+        <v>0.1033046512111345</v>
       </c>
       <c r="T25">
-        <v>1.16997286752887</v>
+        <v>1.182356153595009</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.725893515662296</v>
+        <v>4.528981285843033</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08859825492046219</v>
+        <v>0.08892423559553743</v>
       </c>
       <c r="C26">
-        <v>1978.774972057017</v>
+        <v>1938.103685497771</v>
       </c>
       <c r="D26">
-        <v>2290.078972057017</v>
+        <v>2274.628685497771</v>
       </c>
       <c r="E26">
-        <v>130.004</v>
+        <v>155.225</v>
       </c>
       <c r="F26">
-        <v>605.304</v>
+        <v>630.525</v>
       </c>
       <c r="G26">
         <v>294</v>
@@ -3425,45 +3425,45 @@
         <v>151.6</v>
       </c>
       <c r="M26">
-        <v>33.4733112</v>
+        <v>36.444345</v>
       </c>
       <c r="N26">
-        <v>118.1266888</v>
+        <v>115.155655</v>
       </c>
       <c r="O26">
-        <v>28.350405312</v>
+        <v>27.6373572</v>
       </c>
       <c r="P26">
-        <v>89.77628348799999</v>
+        <v>87.5182978</v>
       </c>
       <c r="Q26">
-        <v>170.876283488</v>
+        <v>168.6182978</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1033046512111345</v>
+        <v>0.1039229807940499</v>
       </c>
       <c r="T26">
-        <v>1.182356153595009</v>
+        <v>1.195069660622913</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.528981285843033</v>
+        <v>4.159767448145933</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08892423559553743</v>
+        <v>0.08948581627061264</v>
       </c>
       <c r="C27">
-        <v>1938.103685497771</v>
+        <v>1886.749140060855</v>
       </c>
       <c r="D27">
-        <v>2274.628685497771</v>
+        <v>2248.495140060855</v>
       </c>
       <c r="E27">
-        <v>155.225</v>
+        <v>180.446</v>
       </c>
       <c r="F27">
-        <v>630.525</v>
+        <v>655.746</v>
       </c>
       <c r="G27">
         <v>294</v>
@@ -3507,45 +3507,45 @@
         <v>151.6</v>
       </c>
       <c r="M27">
-        <v>36.444345</v>
+        <v>40.1972298</v>
       </c>
       <c r="N27">
-        <v>115.155655</v>
+        <v>111.4027702</v>
       </c>
       <c r="O27">
-        <v>27.6373572</v>
+        <v>26.736664848</v>
       </c>
       <c r="P27">
-        <v>87.5182978</v>
+        <v>84.66610535199999</v>
       </c>
       <c r="Q27">
-        <v>168.6182978</v>
+        <v>165.766105352</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1039229807940499</v>
+        <v>0.1045580219873144</v>
       </c>
       <c r="T27">
-        <v>1.195069660622913</v>
+        <v>1.208126775948867</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.159767448145933</v>
+        <v>3.771404167756853</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08948581627061264</v>
+        <v>0.08938239694568786</v>
       </c>
       <c r="C28">
-        <v>1886.749140060855</v>
+        <v>1866.295623331564</v>
       </c>
       <c r="D28">
-        <v>2248.495140060855</v>
+        <v>2253.262623331564</v>
       </c>
       <c r="E28">
-        <v>180.446</v>
+        <v>205.667</v>
       </c>
       <c r="F28">
-        <v>655.746</v>
+        <v>680.967</v>
       </c>
       <c r="G28">
         <v>294</v>
@@ -3589,28 +3589,28 @@
         <v>151.6</v>
       </c>
       <c r="M28">
-        <v>40.1972298</v>
+        <v>41.7432771</v>
       </c>
       <c r="N28">
-        <v>111.4027702</v>
+        <v>109.8567229</v>
       </c>
       <c r="O28">
-        <v>26.736664848</v>
+        <v>26.365613496</v>
       </c>
       <c r="P28">
-        <v>84.66610535199999</v>
+        <v>83.491109404</v>
       </c>
       <c r="Q28">
-        <v>165.766105352</v>
+        <v>164.591109404</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1045580219873144</v>
+        <v>0.1052104615694354</v>
       </c>
       <c r="T28">
-        <v>1.208126775948867</v>
+        <v>1.221541620461834</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.771404167756853</v>
+        <v>3.631722531914007</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08938239694568786</v>
+        <v>0.08927897762076309</v>
       </c>
       <c r="C29">
-        <v>1866.295623331564</v>
+        <v>1845.862366544845</v>
       </c>
       <c r="D29">
-        <v>2253.262623331564</v>
+        <v>2258.050366544845</v>
       </c>
       <c r="E29">
-        <v>205.667</v>
+        <v>230.888</v>
       </c>
       <c r="F29">
-        <v>680.967</v>
+        <v>706.188</v>
       </c>
       <c r="G29">
         <v>294</v>
@@ -3671,28 +3671,28 @@
         <v>151.6</v>
       </c>
       <c r="M29">
-        <v>41.7432771</v>
+        <v>43.2893244</v>
       </c>
       <c r="N29">
-        <v>109.8567229</v>
+        <v>108.3106756</v>
       </c>
       <c r="O29">
-        <v>26.365613496</v>
+        <v>25.994562144</v>
       </c>
       <c r="P29">
-        <v>83.491109404</v>
+        <v>82.316113456</v>
       </c>
       <c r="Q29">
-        <v>164.591109404</v>
+        <v>163.416113456</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1052104615694354</v>
+        <v>0.1058810244732821</v>
       </c>
       <c r="T29">
-        <v>1.221541620461834</v>
+        <v>1.235329099544606</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.631722531914007</v>
+        <v>3.502018155774221</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08927897762076309</v>
+        <v>0.08979267829583831</v>
       </c>
       <c r="C30">
-        <v>1845.862366544845</v>
+        <v>1797.058235442424</v>
       </c>
       <c r="D30">
-        <v>2258.050366544845</v>
+        <v>2234.467235442424</v>
       </c>
       <c r="E30">
-        <v>230.888</v>
+        <v>256.1090000000001</v>
       </c>
       <c r="F30">
-        <v>706.188</v>
+        <v>731.4090000000001</v>
       </c>
       <c r="G30">
         <v>294</v>
@@ -3753,45 +3753,45 @@
         <v>151.6</v>
       </c>
       <c r="M30">
-        <v>43.2893244</v>
+        <v>46.88331690000001</v>
       </c>
       <c r="N30">
-        <v>108.3106756</v>
+        <v>104.7166831</v>
       </c>
       <c r="O30">
-        <v>25.994562144</v>
+        <v>25.13200394399999</v>
       </c>
       <c r="P30">
-        <v>82.316113456</v>
+        <v>79.58467915599999</v>
       </c>
       <c r="Q30">
-        <v>163.416113456</v>
+        <v>160.684679156</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1058810244732821</v>
+        <v>0.1065704764730117</v>
       </c>
       <c r="T30">
-        <v>1.235329099544606</v>
+        <v>1.249504958319851</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.502018155774221</v>
+        <v>3.233559611905359</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08979267829583831</v>
+        <v>0.08971053897091352</v>
       </c>
       <c r="C31">
-        <v>1797.058235442424</v>
+        <v>1775.574972010329</v>
       </c>
       <c r="D31">
-        <v>2234.467235442424</v>
+        <v>2238.20497201033</v>
       </c>
       <c r="E31">
-        <v>256.1089999999999</v>
+        <v>281.33</v>
       </c>
       <c r="F31">
-        <v>731.4089999999999</v>
+        <v>756.63</v>
       </c>
       <c r="G31">
         <v>294</v>
@@ -3835,28 +3835,28 @@
         <v>151.6</v>
       </c>
       <c r="M31">
-        <v>46.8833169</v>
+        <v>48.499983</v>
       </c>
       <c r="N31">
-        <v>104.7166831</v>
+        <v>103.100017</v>
       </c>
       <c r="O31">
-        <v>25.132003944</v>
+        <v>24.74400408</v>
       </c>
       <c r="P31">
-        <v>79.58467915599999</v>
+        <v>78.35601292</v>
       </c>
       <c r="Q31">
-        <v>160.684679156</v>
+        <v>159.45601292</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1065704764730117</v>
+        <v>0.1072796271013051</v>
       </c>
       <c r="T31">
-        <v>1.249504958319851</v>
+        <v>1.26408584163153</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.23355961190536</v>
+        <v>3.125774291508514</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08971053897091352</v>
+        <v>0.08962839964598876</v>
       </c>
       <c r="C32">
-        <v>1775.574972010329</v>
+        <v>1754.104234233772</v>
       </c>
       <c r="D32">
-        <v>2238.20497201033</v>
+        <v>2241.955234233772</v>
       </c>
       <c r="E32">
-        <v>281.33</v>
+        <v>306.551</v>
       </c>
       <c r="F32">
-        <v>756.63</v>
+        <v>781.851</v>
       </c>
       <c r="G32">
         <v>294</v>
@@ -3917,28 +3917,28 @@
         <v>151.6</v>
       </c>
       <c r="M32">
-        <v>48.499983</v>
+        <v>50.1166491</v>
       </c>
       <c r="N32">
-        <v>103.100017</v>
+        <v>101.4833509</v>
       </c>
       <c r="O32">
-        <v>24.74400408</v>
+        <v>24.356004216</v>
       </c>
       <c r="P32">
-        <v>78.35601292</v>
+        <v>77.127346684</v>
       </c>
       <c r="Q32">
-        <v>159.45601292</v>
+        <v>158.227346684</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1072796271013051</v>
+        <v>0.1080093328202736</v>
       </c>
       <c r="T32">
-        <v>1.26408584163153</v>
+        <v>1.2790893592421</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.125774291508514</v>
+        <v>3.024942862750175</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08962839964598876</v>
+        <v>0.09144322032106397</v>
       </c>
       <c r="C33">
-        <v>1754.104234233772</v>
+        <v>1648.847508267519</v>
       </c>
       <c r="D33">
-        <v>2241.955234233772</v>
+        <v>2161.919508267519</v>
       </c>
       <c r="E33">
-        <v>306.551</v>
+        <v>331.772</v>
       </c>
       <c r="F33">
-        <v>781.851</v>
+        <v>807.072</v>
       </c>
       <c r="G33">
         <v>294</v>
@@ -3999,45 +3999,45 @@
         <v>151.6</v>
       </c>
       <c r="M33">
-        <v>50.1166491</v>
+        <v>58.02847680000001</v>
       </c>
       <c r="N33">
-        <v>101.4833509</v>
+        <v>93.57152319999999</v>
       </c>
       <c r="O33">
-        <v>24.356004216</v>
+        <v>22.457165568</v>
       </c>
       <c r="P33">
-        <v>77.127346684</v>
+        <v>71.11435763199999</v>
       </c>
       <c r="Q33">
-        <v>158.227346684</v>
+        <v>152.214357632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1080093328202736</v>
+        <v>0.1087605004721529</v>
       </c>
       <c r="T33">
-        <v>1.2790893592421</v>
+        <v>1.294534156782391</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.024942862750175</v>
+        <v>2.612510414886506</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09144322032106397</v>
+        <v>0.0914203609961392</v>
       </c>
       <c r="C34">
-        <v>1648.847508267519</v>
+        <v>1624.599079646062</v>
       </c>
       <c r="D34">
-        <v>2161.919508267519</v>
+        <v>2162.892079646062</v>
       </c>
       <c r="E34">
-        <v>331.772</v>
+        <v>356.993</v>
       </c>
       <c r="F34">
-        <v>807.072</v>
+        <v>832.293</v>
       </c>
       <c r="G34">
         <v>294</v>
@@ -4081,28 +4081,28 @@
         <v>151.6</v>
       </c>
       <c r="M34">
-        <v>58.02847680000001</v>
+        <v>59.8418667</v>
       </c>
       <c r="N34">
-        <v>93.57152319999999</v>
+        <v>91.7581333</v>
       </c>
       <c r="O34">
-        <v>22.457165568</v>
+        <v>22.021951992</v>
       </c>
       <c r="P34">
-        <v>71.11435763199999</v>
+        <v>69.736181308</v>
       </c>
       <c r="Q34">
-        <v>152.214357632</v>
+        <v>150.836181308</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1087605004721529</v>
+        <v>0.1095340910390137</v>
       </c>
       <c r="T34">
-        <v>1.294534156782391</v>
+        <v>1.310439993055229</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.612510414886506</v>
+        <v>2.533343432617218</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0914203609961392</v>
+        <v>0.09240526167121442</v>
       </c>
       <c r="C35">
-        <v>1624.599079646062</v>
+        <v>1558.252820056548</v>
       </c>
       <c r="D35">
-        <v>2162.892079646062</v>
+        <v>2121.766820056549</v>
       </c>
       <c r="E35">
-        <v>356.993</v>
+        <v>382.214</v>
       </c>
       <c r="F35">
-        <v>832.293</v>
+        <v>857.514</v>
       </c>
       <c r="G35">
         <v>294</v>
@@ -4163,45 +4163,45 @@
         <v>151.6</v>
       </c>
       <c r="M35">
-        <v>59.8418667</v>
+        <v>64.9995612</v>
       </c>
       <c r="N35">
-        <v>91.7581333</v>
+        <v>86.60043879999999</v>
       </c>
       <c r="O35">
-        <v>22.021951992</v>
+        <v>20.784105312</v>
       </c>
       <c r="P35">
-        <v>69.736181308</v>
+        <v>65.816333488</v>
       </c>
       <c r="Q35">
-        <v>150.836181308</v>
+        <v>146.916333488</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1095340910390137</v>
+        <v>0.1103311237442643</v>
       </c>
       <c r="T35">
-        <v>1.310439993055229</v>
+        <v>1.326827824366638</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.533343432617218</v>
+        <v>2.332323437284989</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09240526167121442</v>
+        <v>0.09241204234628965</v>
       </c>
       <c r="C36">
-        <v>1558.252820056548</v>
+        <v>1532.754107761806</v>
       </c>
       <c r="D36">
-        <v>2121.766820056549</v>
+        <v>2121.489107761806</v>
       </c>
       <c r="E36">
-        <v>382.214</v>
+        <v>407.435</v>
       </c>
       <c r="F36">
-        <v>857.514</v>
+        <v>882.735</v>
       </c>
       <c r="G36">
         <v>294</v>
@@ -4245,28 +4245,28 @@
         <v>151.6</v>
       </c>
       <c r="M36">
-        <v>64.9995612</v>
+        <v>66.91131300000001</v>
       </c>
       <c r="N36">
-        <v>86.60043879999999</v>
+        <v>84.68868699999999</v>
       </c>
       <c r="O36">
-        <v>20.784105312</v>
+        <v>20.32528487999999</v>
       </c>
       <c r="P36">
-        <v>65.816333488</v>
+        <v>64.36340211999999</v>
       </c>
       <c r="Q36">
-        <v>146.916333488</v>
+        <v>145.46340212</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1103311237442643</v>
+        <v>0.1111526805327533</v>
       </c>
       <c r="T36">
-        <v>1.326827824366638</v>
+        <v>1.343719896641475</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.332323437284989</v>
+        <v>2.265685624791132</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09241204234628965</v>
+        <v>0.09241882302136488</v>
       </c>
       <c r="C37">
-        <v>1532.754107761806</v>
+        <v>1507.255468155564</v>
       </c>
       <c r="D37">
-        <v>2121.489107761806</v>
+        <v>2121.211468155564</v>
       </c>
       <c r="E37">
-        <v>407.435</v>
+        <v>432.656</v>
       </c>
       <c r="F37">
-        <v>882.735</v>
+        <v>907.956</v>
       </c>
       <c r="G37">
         <v>294</v>
@@ -4327,28 +4327,28 @@
         <v>151.6</v>
       </c>
       <c r="M37">
-        <v>66.91131300000001</v>
+        <v>68.82306480000001</v>
       </c>
       <c r="N37">
-        <v>84.68868699999999</v>
+        <v>82.77693519999998</v>
       </c>
       <c r="O37">
-        <v>20.32528487999999</v>
+        <v>19.866464448</v>
       </c>
       <c r="P37">
-        <v>64.36340211999999</v>
+        <v>62.91047075199999</v>
       </c>
       <c r="Q37">
-        <v>145.46340212</v>
+        <v>144.010470752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1111526805327533</v>
+        <v>0.1119999109708826</v>
       </c>
       <c r="T37">
-        <v>1.343719896641475</v>
+        <v>1.3611398461749</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.265685624791132</v>
+        <v>2.202749912991378</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09241882302136489</v>
+        <v>0.0924256036964401</v>
       </c>
       <c r="C38">
-        <v>1507.255468155564</v>
+        <v>1481.756901209292</v>
       </c>
       <c r="D38">
-        <v>2121.211468155564</v>
+        <v>2120.933901209291</v>
       </c>
       <c r="E38">
-        <v>432.6559999999999</v>
+        <v>457.8769999999999</v>
       </c>
       <c r="F38">
-        <v>907.9559999999999</v>
+        <v>933.1769999999999</v>
       </c>
       <c r="G38">
         <v>294</v>
@@ -4409,28 +4409,28 @@
         <v>151.6</v>
       </c>
       <c r="M38">
-        <v>68.8230648</v>
+        <v>70.7348166</v>
       </c>
       <c r="N38">
-        <v>82.7769352</v>
+        <v>80.86518339999999</v>
       </c>
       <c r="O38">
-        <v>19.866464448</v>
+        <v>19.407644016</v>
       </c>
       <c r="P38">
-        <v>62.91047075199999</v>
+        <v>61.45753938399999</v>
       </c>
       <c r="Q38">
-        <v>144.010470752</v>
+        <v>142.557539384</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1119999109708826</v>
+        <v>0.112874037613397</v>
       </c>
       <c r="T38">
-        <v>1.3611398461749</v>
+        <v>1.379112809979227</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.202749912991378</v>
+        <v>2.143216131559179</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0924256036964401</v>
+        <v>0.09243238437151532</v>
       </c>
       <c r="C39">
-        <v>1481.756901209292</v>
+        <v>1456.258406894464</v>
       </c>
       <c r="D39">
-        <v>2120.933901209291</v>
+        <v>2120.656406894464</v>
       </c>
       <c r="E39">
-        <v>457.8769999999999</v>
+        <v>483.098</v>
       </c>
       <c r="F39">
-        <v>933.1769999999999</v>
+        <v>958.398</v>
       </c>
       <c r="G39">
         <v>294</v>
@@ -4491,28 +4491,28 @@
         <v>151.6</v>
       </c>
       <c r="M39">
-        <v>70.7348166</v>
+        <v>72.64656840000001</v>
       </c>
       <c r="N39">
-        <v>80.86518339999999</v>
+        <v>78.95343159999999</v>
       </c>
       <c r="O39">
-        <v>19.407644016</v>
+        <v>18.948823584</v>
       </c>
       <c r="P39">
-        <v>61.45753938399999</v>
+        <v>60.00460801599999</v>
       </c>
       <c r="Q39">
-        <v>142.557539384</v>
+        <v>141.104608016</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.112874037613397</v>
+        <v>0.1137763618895409</v>
       </c>
       <c r="T39">
-        <v>1.379112809979227</v>
+        <v>1.397665546809501</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.143216131559179</v>
+        <v>2.086815707044464</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09243238437151532</v>
+        <v>0.09243916504659057</v>
       </c>
       <c r="C40">
-        <v>1456.258406894464</v>
+        <v>1430.75998518258</v>
       </c>
       <c r="D40">
-        <v>2120.656406894464</v>
+        <v>2120.37898518258</v>
       </c>
       <c r="E40">
-        <v>483.098</v>
+        <v>508.319</v>
       </c>
       <c r="F40">
-        <v>958.398</v>
+        <v>983.619</v>
       </c>
       <c r="G40">
         <v>294</v>
@@ -4573,28 +4573,28 @@
         <v>151.6</v>
       </c>
       <c r="M40">
-        <v>72.64656840000001</v>
+        <v>74.55832020000001</v>
       </c>
       <c r="N40">
-        <v>78.95343159999999</v>
+        <v>77.04167979999998</v>
       </c>
       <c r="O40">
-        <v>18.948823584</v>
+        <v>18.490003152</v>
       </c>
       <c r="P40">
-        <v>60.00460801599999</v>
+        <v>58.55167664799998</v>
       </c>
       <c r="Q40">
-        <v>141.104608016</v>
+        <v>139.651676648</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1137763618895409</v>
+        <v>0.1147082705681813</v>
       </c>
       <c r="T40">
-        <v>1.397665546809501</v>
+        <v>1.416826570093226</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.086815707044464</v>
+        <v>2.033307611992041</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09243916504659057</v>
+        <v>0.09676274572166579</v>
       </c>
       <c r="C41">
-        <v>1430.75998518258</v>
+        <v>1242.286545874014</v>
       </c>
       <c r="D41">
-        <v>2120.37898518258</v>
+        <v>1957.126545874014</v>
       </c>
       <c r="E41">
-        <v>508.319</v>
+        <v>533.54</v>
       </c>
       <c r="F41">
-        <v>983.619</v>
+        <v>1008.84</v>
       </c>
       <c r="G41">
         <v>294</v>
@@ -4655,45 +4655,45 @@
         <v>151.6</v>
       </c>
       <c r="M41">
-        <v>74.55832020000001</v>
+        <v>90.79559999999999</v>
       </c>
       <c r="N41">
-        <v>77.04167979999998</v>
+        <v>60.8044</v>
       </c>
       <c r="O41">
-        <v>18.490003152</v>
+        <v>14.593056</v>
       </c>
       <c r="P41">
-        <v>58.55167664799998</v>
+        <v>46.211344</v>
       </c>
       <c r="Q41">
-        <v>139.651676648</v>
+        <v>127.311344</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1147082705681813</v>
+        <v>0.115671242869443</v>
       </c>
       <c r="T41">
-        <v>1.416826570093226</v>
+        <v>1.436626294153076</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.033307611992041</v>
+        <v>1.669684434047465</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09676274572166579</v>
+        <v>0.09687744639674101</v>
       </c>
       <c r="C42">
-        <v>1242.286545874014</v>
+        <v>1213.076203157438</v>
       </c>
       <c r="D42">
-        <v>1957.126545874014</v>
+        <v>1953.137203157438</v>
       </c>
       <c r="E42">
-        <v>533.54</v>
+        <v>558.7610000000002</v>
       </c>
       <c r="F42">
-        <v>1008.84</v>
+        <v>1034.061</v>
       </c>
       <c r="G42">
         <v>294</v>
@@ -4737,28 +4737,28 @@
         <v>151.6</v>
       </c>
       <c r="M42">
-        <v>90.79559999999999</v>
+        <v>93.06549000000001</v>
       </c>
       <c r="N42">
-        <v>60.8044</v>
+        <v>58.53450999999998</v>
       </c>
       <c r="O42">
-        <v>14.593056</v>
+        <v>14.0482824</v>
       </c>
       <c r="P42">
-        <v>46.211344</v>
+        <v>44.48622759999999</v>
       </c>
       <c r="Q42">
-        <v>127.311344</v>
+        <v>125.5862276</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.115671242869443</v>
+        <v>0.116666858299561</v>
       </c>
       <c r="T42">
-        <v>1.436626294153076</v>
+        <v>1.4570971952997</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.669684434047465</v>
+        <v>1.628960423460941</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09687744639674101</v>
+        <v>0.09699214707181623</v>
       </c>
       <c r="C43">
-        <v>1213.076203157438</v>
+        <v>1183.882090848664</v>
       </c>
       <c r="D43">
-        <v>1953.137203157438</v>
+        <v>1949.164090848665</v>
       </c>
       <c r="E43">
-        <v>558.7610000000002</v>
+        <v>583.9820000000002</v>
       </c>
       <c r="F43">
-        <v>1034.061</v>
+        <v>1059.282</v>
       </c>
       <c r="G43">
         <v>294</v>
@@ -4819,28 +4819,28 @@
         <v>151.6</v>
       </c>
       <c r="M43">
-        <v>93.06549000000001</v>
+        <v>95.33538000000001</v>
       </c>
       <c r="N43">
-        <v>58.53450999999998</v>
+        <v>56.26461999999998</v>
       </c>
       <c r="O43">
-        <v>14.0482824</v>
+        <v>13.5035088</v>
       </c>
       <c r="P43">
-        <v>44.48622759999999</v>
+        <v>42.76111119999999</v>
       </c>
       <c r="Q43">
-        <v>125.5862276</v>
+        <v>123.8611112</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.116666858299561</v>
+        <v>0.1176968052962349</v>
       </c>
       <c r="T43">
-        <v>1.4570971952997</v>
+        <v>1.478273989589311</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.628960423460941</v>
+        <v>1.590175651473776</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09699214707181625</v>
+        <v>0.09710684774689146</v>
       </c>
       <c r="C44">
-        <v>1183.882090848664</v>
+        <v>1154.704110100073</v>
       </c>
       <c r="D44">
-        <v>1949.164090848664</v>
+        <v>1945.207110100073</v>
       </c>
       <c r="E44">
-        <v>583.982</v>
+        <v>609.203</v>
       </c>
       <c r="F44">
-        <v>1059.282</v>
+        <v>1084.503</v>
       </c>
       <c r="G44">
         <v>294</v>
@@ -4901,28 +4901,28 @@
         <v>151.6</v>
       </c>
       <c r="M44">
-        <v>95.33537999999999</v>
+        <v>97.60526999999999</v>
       </c>
       <c r="N44">
-        <v>56.26462000000001</v>
+        <v>53.99473</v>
       </c>
       <c r="O44">
-        <v>13.5035088</v>
+        <v>12.9587352</v>
       </c>
       <c r="P44">
-        <v>42.76111120000001</v>
+        <v>41.0359948</v>
       </c>
       <c r="Q44">
-        <v>123.8611112</v>
+        <v>122.1359948</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1176968052962349</v>
+        <v>0.1187628907840201</v>
       </c>
       <c r="T44">
-        <v>1.478273989589311</v>
+        <v>1.500193829292592</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.590175651473776</v>
+        <v>1.553194822369735</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09710684774689146</v>
+        <v>0.09722154842196666</v>
       </c>
       <c r="C45">
-        <v>1154.704110100073</v>
+        <v>1125.542162865095</v>
       </c>
       <c r="D45">
-        <v>1945.207110100073</v>
+        <v>1941.266162865095</v>
       </c>
       <c r="E45">
-        <v>609.203</v>
+        <v>634.424</v>
       </c>
       <c r="F45">
-        <v>1084.503</v>
+        <v>1109.724</v>
       </c>
       <c r="G45">
         <v>294</v>
@@ -4983,28 +4983,28 @@
         <v>151.6</v>
       </c>
       <c r="M45">
-        <v>97.60526999999999</v>
+        <v>99.87515999999999</v>
       </c>
       <c r="N45">
-        <v>53.99473</v>
+        <v>51.72484</v>
       </c>
       <c r="O45">
-        <v>12.9587352</v>
+        <v>12.4139616</v>
       </c>
       <c r="P45">
-        <v>41.0359948</v>
+        <v>39.3108784</v>
       </c>
       <c r="Q45">
-        <v>122.1359948</v>
+        <v>120.4108784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1187628907840201</v>
+        <v>0.1198670507535119</v>
       </c>
       <c r="T45">
-        <v>1.500193829292592</v>
+        <v>1.522896520413848</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.553194822369735</v>
+        <v>1.51789494004315</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09722154842196666</v>
+        <v>0.1186413897503886</v>
       </c>
       <c r="C46">
-        <v>1125.542162865095</v>
+        <v>567.4613020895747</v>
       </c>
       <c r="D46">
-        <v>1941.266162865095</v>
+        <v>1408.406302089575</v>
       </c>
       <c r="E46">
-        <v>634.424</v>
+        <v>659.645</v>
       </c>
       <c r="F46">
-        <v>1109.724</v>
+        <v>1134.945</v>
       </c>
       <c r="G46">
         <v>294</v>
@@ -5065,45 +5065,45 @@
         <v>151.6</v>
       </c>
       <c r="M46">
-        <v>99.87515999999999</v>
+        <v>166.609926</v>
       </c>
       <c r="N46">
-        <v>51.72484</v>
+        <v>-15.00992600000001</v>
       </c>
       <c r="O46">
-        <v>12.4139616</v>
+        <v>-3.602382240000002</v>
       </c>
       <c r="P46">
-        <v>39.3108784</v>
+        <v>-11.40754376000001</v>
       </c>
       <c r="Q46">
-        <v>120.4108784</v>
+        <v>69.69245623999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1198670507535119</v>
+        <v>0.121831751382834</v>
       </c>
       <c r="T46">
-        <v>1.522896520413848</v>
+        <v>1.563292833235952</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.24</v>
+        <v>0.2183783455974886</v>
       </c>
       <c r="W46">
-        <v>0.0684</v>
+        <v>0.1147420588662887</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.51789494004315</v>
+        <v>0.909909773322869</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1186413897503886</v>
+        <v>0.1196513897503886</v>
       </c>
       <c r="C47">
-        <v>567.4613020895747</v>
+        <v>524.2443004865643</v>
       </c>
       <c r="D47">
-        <v>1408.406302089575</v>
+        <v>1390.410300486564</v>
       </c>
       <c r="E47">
-        <v>659.645</v>
+        <v>684.866</v>
       </c>
       <c r="F47">
-        <v>1134.945</v>
+        <v>1160.166</v>
       </c>
       <c r="G47">
         <v>294</v>
@@ -5147,37 +5147,37 @@
         <v>151.6</v>
       </c>
       <c r="M47">
-        <v>166.609926</v>
+        <v>170.3123688</v>
       </c>
       <c r="N47">
-        <v>-15.00992600000001</v>
+        <v>-18.71236880000001</v>
       </c>
       <c r="O47">
-        <v>-3.602382240000002</v>
+        <v>-4.490968512000001</v>
       </c>
       <c r="P47">
-        <v>-11.40754376000001</v>
+        <v>-14.22140028800001</v>
       </c>
       <c r="Q47">
-        <v>69.69245623999998</v>
+        <v>66.87859971199998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.121831751382834</v>
+        <v>0.1232397467788124</v>
       </c>
       <c r="T47">
-        <v>1.563292833235952</v>
+        <v>1.5922427005181</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2183783455974886</v>
+        <v>0.2136309902584127</v>
       </c>
       <c r="W47">
-        <v>0.1147420588662887</v>
+        <v>0.115438970630065</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.909909773322869</v>
+        <v>0.8901291260767198</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1196513897503886</v>
+        <v>0.1206613897503886</v>
       </c>
       <c r="C48">
-        <v>524.2443004865643</v>
+        <v>481.4813868682097</v>
       </c>
       <c r="D48">
-        <v>1390.410300486564</v>
+        <v>1372.86838686821</v>
       </c>
       <c r="E48">
-        <v>684.866</v>
+        <v>710.087</v>
       </c>
       <c r="F48">
-        <v>1160.166</v>
+        <v>1185.387</v>
       </c>
       <c r="G48">
         <v>294</v>
@@ -5229,37 +5229,37 @@
         <v>151.6</v>
       </c>
       <c r="M48">
-        <v>170.3123688</v>
+        <v>174.0148116</v>
       </c>
       <c r="N48">
-        <v>-18.71236880000001</v>
+        <v>-22.41481160000001</v>
       </c>
       <c r="O48">
-        <v>-4.490968512000001</v>
+        <v>-5.379554784000002</v>
       </c>
       <c r="P48">
-        <v>-14.22140028800001</v>
+        <v>-17.03525681600001</v>
       </c>
       <c r="Q48">
-        <v>66.87859971199998</v>
+        <v>64.06474318399998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1232397467788124</v>
+        <v>0.1247008740765259</v>
       </c>
       <c r="T48">
-        <v>1.5922427005181</v>
+        <v>1.622285015622215</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2136309902584127</v>
+        <v>0.2090856500401486</v>
       </c>
       <c r="W48">
-        <v>0.115438970630065</v>
+        <v>0.1161062265741062</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8901291260767198</v>
+        <v>0.8711902085006193</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1206613897503886</v>
+        <v>0.1216713897503886</v>
       </c>
       <c r="C49">
-        <v>481.4813868682097</v>
+        <v>439.155588558614</v>
       </c>
       <c r="D49">
-        <v>1372.86838686821</v>
+        <v>1355.763588558614</v>
       </c>
       <c r="E49">
-        <v>710.087</v>
+        <v>735.308</v>
       </c>
       <c r="F49">
-        <v>1185.387</v>
+        <v>1210.608</v>
       </c>
       <c r="G49">
         <v>294</v>
@@ -5311,37 +5311,37 @@
         <v>151.6</v>
       </c>
       <c r="M49">
-        <v>174.0148116</v>
+        <v>177.7172544</v>
       </c>
       <c r="N49">
-        <v>-22.41481160000001</v>
+        <v>-26.11725440000001</v>
       </c>
       <c r="O49">
-        <v>-5.379554784000002</v>
+        <v>-6.268141056000002</v>
       </c>
       <c r="P49">
-        <v>-17.03525681600001</v>
+        <v>-19.84911334400001</v>
       </c>
       <c r="Q49">
-        <v>64.06474318399998</v>
+        <v>61.25088665599999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1247008740765259</v>
+        <v>0.1262181985779975</v>
       </c>
       <c r="T49">
-        <v>1.622285015622215</v>
+        <v>1.65348280438418</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2090856500401486</v>
+        <v>0.2047296989976455</v>
       </c>
       <c r="W49">
-        <v>0.1161062265741062</v>
+        <v>0.1167456801871457</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8711902085006193</v>
+        <v>0.8530404124901898</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1216713897503886</v>
+        <v>0.1226813897503886</v>
       </c>
       <c r="C50">
-        <v>439.155588558614</v>
+        <v>397.2507683345416</v>
       </c>
       <c r="D50">
-        <v>1355.763588558614</v>
+        <v>1339.079768334542</v>
       </c>
       <c r="E50">
-        <v>735.308</v>
+        <v>760.529</v>
       </c>
       <c r="F50">
-        <v>1210.608</v>
+        <v>1235.829</v>
       </c>
       <c r="G50">
         <v>294</v>
@@ -5393,37 +5393,37 @@
         <v>151.6</v>
       </c>
       <c r="M50">
-        <v>177.7172544</v>
+        <v>181.4196972</v>
       </c>
       <c r="N50">
-        <v>-26.11725440000001</v>
+        <v>-29.81969720000001</v>
       </c>
       <c r="O50">
-        <v>-6.268141056000002</v>
+        <v>-7.156727328000001</v>
       </c>
       <c r="P50">
-        <v>-19.84911334400001</v>
+        <v>-22.66296987200001</v>
       </c>
       <c r="Q50">
-        <v>61.25088665599999</v>
+        <v>58.43703012799999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1262181985779975</v>
+        <v>0.1277950260010955</v>
       </c>
       <c r="T50">
-        <v>1.65348280438418</v>
+        <v>1.685904035842694</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2047296989976455</v>
+        <v>0.2005515418752446</v>
       </c>
       <c r="W50">
-        <v>0.1167456801871457</v>
+        <v>0.1173590336527141</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8530404124901898</v>
+        <v>0.8356314244801859</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1226813897503886</v>
+        <v>0.1236913897503886</v>
       </c>
       <c r="C51">
-        <v>397.2507683345416</v>
+        <v>355.7515736455355</v>
       </c>
       <c r="D51">
-        <v>1339.079768334542</v>
+        <v>1322.801573645535</v>
       </c>
       <c r="E51">
-        <v>760.529</v>
+        <v>785.75</v>
       </c>
       <c r="F51">
-        <v>1235.829</v>
+        <v>1261.05</v>
       </c>
       <c r="G51">
         <v>294</v>
@@ -5475,37 +5475,37 @@
         <v>151.6</v>
       </c>
       <c r="M51">
-        <v>181.4196972</v>
+        <v>185.12214</v>
       </c>
       <c r="N51">
-        <v>-29.81969720000001</v>
+        <v>-33.52214000000001</v>
       </c>
       <c r="O51">
-        <v>-7.156727328000001</v>
+        <v>-8.045313600000002</v>
       </c>
       <c r="P51">
-        <v>-22.66296987200001</v>
+        <v>-25.47682640000001</v>
       </c>
       <c r="Q51">
-        <v>58.43703012799999</v>
+        <v>55.62317359999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1277950260010955</v>
+        <v>0.1294349265211174</v>
       </c>
       <c r="T51">
-        <v>1.685904035842694</v>
+        <v>1.719622116559547</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2005515418752446</v>
+        <v>0.1965405110377397</v>
       </c>
       <c r="W51">
-        <v>0.1173590336527141</v>
+        <v>0.1179478529796598</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8356314244801859</v>
+        <v>0.8189187959905821</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1236913897503886</v>
+        <v>0.1247013897503886</v>
       </c>
       <c r="C52">
-        <v>355.7515736455355</v>
+        <v>314.6433894933211</v>
       </c>
       <c r="D52">
-        <v>1322.801573645535</v>
+        <v>1306.914389493321</v>
       </c>
       <c r="E52">
-        <v>785.75</v>
+        <v>810.971</v>
       </c>
       <c r="F52">
-        <v>1261.05</v>
+        <v>1286.271</v>
       </c>
       <c r="G52">
         <v>294</v>
@@ -5557,37 +5557,37 @@
         <v>151.6</v>
       </c>
       <c r="M52">
-        <v>185.12214</v>
+        <v>188.8245828</v>
       </c>
       <c r="N52">
-        <v>-33.52214000000001</v>
+        <v>-37.22458280000001</v>
       </c>
       <c r="O52">
-        <v>-8.045313600000002</v>
+        <v>-8.933899872000001</v>
       </c>
       <c r="P52">
-        <v>-25.47682640000001</v>
+        <v>-28.29068292800001</v>
       </c>
       <c r="Q52">
-        <v>55.62317359999999</v>
+        <v>52.80931707199998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1294349265211174</v>
+        <v>0.1311417617562423</v>
       </c>
       <c r="T52">
-        <v>1.719622116559547</v>
+        <v>1.754716445468926</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1965405110377397</v>
+        <v>0.1926867755271958</v>
       </c>
       <c r="W52">
-        <v>0.1179478529796598</v>
+        <v>0.1185135813526077</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8189187959905821</v>
+        <v>0.8028615646966492</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1247013897503886</v>
+        <v>0.1550169464970883</v>
       </c>
       <c r="C53">
-        <v>314.6433894933211</v>
+        <v>-56.87350648739061</v>
       </c>
       <c r="D53">
-        <v>1306.914389493321</v>
+        <v>960.6184935126093</v>
       </c>
       <c r="E53">
-        <v>810.971</v>
+        <v>836.192</v>
       </c>
       <c r="F53">
-        <v>1286.271</v>
+        <v>1311.492</v>
       </c>
       <c r="G53">
         <v>294</v>
@@ -5639,45 +5639,45 @@
         <v>151.6</v>
       </c>
       <c r="M53">
-        <v>188.8245828</v>
+        <v>263.3475936</v>
       </c>
       <c r="N53">
-        <v>-37.22458280000001</v>
+        <v>-111.7475936</v>
       </c>
       <c r="O53">
-        <v>-8.933899872000001</v>
+        <v>-26.819422464</v>
       </c>
       <c r="P53">
-        <v>-28.29068292800001</v>
+        <v>-84.92817113599999</v>
       </c>
       <c r="Q53">
-        <v>52.80931707199998</v>
+        <v>-3.828171135999995</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1311417617562423</v>
+        <v>0.135472958348455</v>
       </c>
       <c r="T53">
-        <v>1.754716445468926</v>
+        <v>1.843770406068219</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1926867755271958</v>
+        <v>0.1381596068626465</v>
       </c>
       <c r="W53">
-        <v>0.1185135813526077</v>
+        <v>0.1730575509419806</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8028615646966492</v>
+        <v>0.5756650285943604</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1550169464970883</v>
+        <v>0.1565669464970883</v>
       </c>
       <c r="C54">
-        <v>-56.87350648739061</v>
+        <v>-94.93474511858653</v>
       </c>
       <c r="D54">
-        <v>960.6184935126093</v>
+        <v>947.7782548814134</v>
       </c>
       <c r="E54">
-        <v>836.192</v>
+        <v>861.413</v>
       </c>
       <c r="F54">
-        <v>1311.492</v>
+        <v>1336.713</v>
       </c>
       <c r="G54">
         <v>294</v>
@@ -5721,37 +5721,37 @@
         <v>151.6</v>
       </c>
       <c r="M54">
-        <v>263.3475936</v>
+        <v>268.4119704</v>
       </c>
       <c r="N54">
-        <v>-111.7475936</v>
+        <v>-116.8119704</v>
       </c>
       <c r="O54">
-        <v>-26.819422464</v>
+        <v>-28.03487289600001</v>
       </c>
       <c r="P54">
-        <v>-84.92817113599999</v>
+        <v>-88.77709750400003</v>
       </c>
       <c r="Q54">
-        <v>-3.828171135999995</v>
+        <v>-7.677097504000031</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.135472958348455</v>
+        <v>0.1373808936324647</v>
       </c>
       <c r="T54">
-        <v>1.843770406068219</v>
+        <v>1.882999563644139</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1381596068626465</v>
+        <v>0.1355528218275022</v>
       </c>
       <c r="W54">
-        <v>0.1730575509419806</v>
+        <v>0.1735809933770376</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5756650285943604</v>
+        <v>0.5648034242812592</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1565669464970883</v>
+        <v>0.1581169464970883</v>
       </c>
       <c r="C55">
-        <v>-94.93474511858653</v>
+        <v>-132.6572498668518</v>
       </c>
       <c r="D55">
-        <v>947.7782548814134</v>
+        <v>935.2767501331482</v>
       </c>
       <c r="E55">
-        <v>861.413</v>
+        <v>886.634</v>
       </c>
       <c r="F55">
-        <v>1336.713</v>
+        <v>1361.934</v>
       </c>
       <c r="G55">
         <v>294</v>
@@ -5803,37 +5803,37 @@
         <v>151.6</v>
       </c>
       <c r="M55">
-        <v>268.4119704</v>
+        <v>273.4763472</v>
       </c>
       <c r="N55">
-        <v>-116.8119704</v>
+        <v>-121.8763472</v>
       </c>
       <c r="O55">
-        <v>-28.03487289600001</v>
+        <v>-29.250323328</v>
       </c>
       <c r="P55">
-        <v>-88.77709750400003</v>
+        <v>-92.62602387200002</v>
       </c>
       <c r="Q55">
-        <v>-7.677097504000031</v>
+        <v>-11.52602387200002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1373808936324647</v>
+        <v>0.1393717826244748</v>
       </c>
       <c r="T55">
-        <v>1.882999563644139</v>
+        <v>1.923934336766838</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1355528218275022</v>
+        <v>0.1330425843862522</v>
       </c>
       <c r="W55">
-        <v>0.1735809933770376</v>
+        <v>0.1740850490552406</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5648034242812592</v>
+        <v>0.554344101609384</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1581169464970883</v>
+        <v>0.1596669464970883</v>
       </c>
       <c r="C56">
-        <v>-132.6572498668518</v>
+        <v>-170.054250262029</v>
       </c>
       <c r="D56">
-        <v>935.2767501331482</v>
+        <v>923.100749737971</v>
       </c>
       <c r="E56">
-        <v>886.634</v>
+        <v>911.855</v>
       </c>
       <c r="F56">
-        <v>1361.934</v>
+        <v>1387.155</v>
       </c>
       <c r="G56">
         <v>294</v>
@@ -5885,37 +5885,37 @@
         <v>151.6</v>
       </c>
       <c r="M56">
-        <v>273.4763472</v>
+        <v>278.540724</v>
       </c>
       <c r="N56">
-        <v>-121.8763472</v>
+        <v>-126.940724</v>
       </c>
       <c r="O56">
-        <v>-29.250323328</v>
+        <v>-30.46577376</v>
       </c>
       <c r="P56">
-        <v>-92.62602387200002</v>
+        <v>-96.47495024000001</v>
       </c>
       <c r="Q56">
-        <v>-11.52602387200002</v>
+        <v>-15.37495024000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1393717826244748</v>
+        <v>0.1414511555716853</v>
       </c>
       <c r="T56">
-        <v>1.923934336766838</v>
+        <v>1.966688433139434</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1330425843862522</v>
+        <v>0.1306236283065021</v>
       </c>
       <c r="W56">
-        <v>0.1740850490552406</v>
+        <v>0.1745707754360544</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.554344101609384</v>
+        <v>0.5442651179437589</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1596669464970883</v>
+        <v>0.1612169464970883</v>
       </c>
       <c r="C57">
-        <v>-170.054250262029</v>
+        <v>-207.1382957672852</v>
       </c>
       <c r="D57">
-        <v>923.100749737971</v>
+        <v>911.2377042327148</v>
       </c>
       <c r="E57">
-        <v>911.855</v>
+        <v>937.076</v>
       </c>
       <c r="F57">
-        <v>1387.155</v>
+        <v>1412.376</v>
       </c>
       <c r="G57">
         <v>294</v>
@@ -5967,37 +5967,37 @@
         <v>151.6</v>
       </c>
       <c r="M57">
-        <v>278.540724</v>
+        <v>283.6051008</v>
       </c>
       <c r="N57">
-        <v>-126.940724</v>
+        <v>-132.0051008</v>
       </c>
       <c r="O57">
-        <v>-30.46577376</v>
+        <v>-31.681224192</v>
       </c>
       <c r="P57">
-        <v>-96.47495024000001</v>
+        <v>-100.323876608</v>
       </c>
       <c r="Q57">
-        <v>-15.37495024000002</v>
+        <v>-19.22387660800001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1414511555716853</v>
+        <v>0.1436250454710418</v>
       </c>
       <c r="T57">
-        <v>1.966688433139434</v>
+        <v>2.011385897528966</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1306236283065021</v>
+        <v>0.1282910635153146</v>
       </c>
       <c r="W57">
-        <v>0.1745707754360544</v>
+        <v>0.1750391544461248</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5442651179437589</v>
+        <v>0.5345460979804775</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1612169464970883</v>
+        <v>0.1627669464970883</v>
       </c>
       <c r="C58">
-        <v>-207.1382957672852</v>
+        <v>-243.9212989233606</v>
       </c>
       <c r="D58">
-        <v>911.2377042327148</v>
+        <v>899.6757010766396</v>
       </c>
       <c r="E58">
-        <v>937.076</v>
+        <v>962.2970000000003</v>
       </c>
       <c r="F58">
-        <v>1412.376</v>
+        <v>1437.597</v>
       </c>
       <c r="G58">
         <v>294</v>
@@ -6049,37 +6049,37 @@
         <v>151.6</v>
       </c>
       <c r="M58">
-        <v>283.6051008</v>
+        <v>288.6694776000001</v>
       </c>
       <c r="N58">
-        <v>-132.0051008</v>
+        <v>-137.0694776000001</v>
       </c>
       <c r="O58">
-        <v>-31.681224192</v>
+        <v>-32.89667462400001</v>
       </c>
       <c r="P58">
-        <v>-100.323876608</v>
+        <v>-104.172802976</v>
       </c>
       <c r="Q58">
-        <v>-19.22387660800001</v>
+        <v>-23.07280297600005</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1436250454710418</v>
+        <v>0.1459000465285079</v>
       </c>
       <c r="T58">
-        <v>2.011385897528966</v>
+        <v>2.058162313750571</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1282910635153146</v>
+        <v>0.1260403431027652</v>
       </c>
       <c r="W58">
-        <v>0.1750391544461248</v>
+        <v>0.1754910991049647</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5345460979804775</v>
+        <v>0.5251680962615217</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1627669464970883</v>
+        <v>0.1643169464970883</v>
       </c>
       <c r="C59">
-        <v>-243.9212989233606</v>
+        <v>-280.4145752494187</v>
       </c>
       <c r="D59">
-        <v>899.6757010766396</v>
+        <v>888.4034247505815</v>
       </c>
       <c r="E59">
-        <v>962.2970000000003</v>
+        <v>987.5180000000003</v>
       </c>
       <c r="F59">
-        <v>1437.597</v>
+        <v>1462.818</v>
       </c>
       <c r="G59">
         <v>294</v>
@@ -6131,37 +6131,37 @@
         <v>151.6</v>
       </c>
       <c r="M59">
-        <v>288.6694776000001</v>
+        <v>293.7338544</v>
       </c>
       <c r="N59">
-        <v>-137.0694776000001</v>
+        <v>-142.1338544</v>
       </c>
       <c r="O59">
-        <v>-32.89667462400001</v>
+        <v>-34.11212505600001</v>
       </c>
       <c r="P59">
-        <v>-104.172802976</v>
+        <v>-108.021729344</v>
       </c>
       <c r="Q59">
-        <v>-23.07280297600005</v>
+        <v>-26.92172934400004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1459000465285079</v>
+        <v>0.1482833809696629</v>
       </c>
       <c r="T59">
-        <v>2.058162313750571</v>
+        <v>2.10716617836368</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1260403431027652</v>
+        <v>0.1238672337389244</v>
       </c>
       <c r="W59">
-        <v>0.1754910991049647</v>
+        <v>0.175927459465224</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5251680962615217</v>
+        <v>0.5161134739121851</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1643169464970883</v>
+        <v>0.1658669464970883</v>
       </c>
       <c r="C60">
-        <v>-280.4145752494178</v>
+        <v>-316.6288801814494</v>
       </c>
       <c r="D60">
-        <v>888.4034247505818</v>
+        <v>877.4101198185505</v>
       </c>
       <c r="E60">
-        <v>987.5179999999998</v>
+        <v>1012.739</v>
       </c>
       <c r="F60">
-        <v>1462.818</v>
+        <v>1488.039</v>
       </c>
       <c r="G60">
         <v>294</v>
@@ -6213,37 +6213,37 @@
         <v>151.6</v>
       </c>
       <c r="M60">
-        <v>293.7338544</v>
+        <v>298.7982312</v>
       </c>
       <c r="N60">
-        <v>-142.1338544</v>
+        <v>-147.1982312</v>
       </c>
       <c r="O60">
-        <v>-34.112125056</v>
+        <v>-35.32757548799999</v>
       </c>
       <c r="P60">
-        <v>-108.021729344</v>
+        <v>-111.870655712</v>
       </c>
       <c r="Q60">
-        <v>-26.921729344</v>
+        <v>-30.77065571199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1482833809696629</v>
+        <v>0.1507829756274595</v>
       </c>
       <c r="T60">
-        <v>2.107166178363679</v>
+        <v>2.158560475396939</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1238672337389244</v>
+        <v>0.1217677890992817</v>
       </c>
       <c r="W60">
-        <v>0.175927459465224</v>
+        <v>0.1763490279488643</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5161134739121852</v>
+        <v>0.5073657879136736</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1658669464970883</v>
+        <v>0.1889114734474655</v>
       </c>
       <c r="C61">
-        <v>-316.6288801814494</v>
+        <v>-478.1872718795432</v>
       </c>
       <c r="D61">
-        <v>877.4101198185505</v>
+        <v>741.0727281204566</v>
       </c>
       <c r="E61">
-        <v>1012.739</v>
+        <v>1037.96</v>
       </c>
       <c r="F61">
-        <v>1488.039</v>
+        <v>1513.26</v>
       </c>
       <c r="G61">
         <v>294</v>
@@ -6295,45 +6295,45 @@
         <v>151.6</v>
       </c>
       <c r="M61">
-        <v>298.7982312</v>
+        <v>356.826708</v>
       </c>
       <c r="N61">
-        <v>-147.1982312</v>
+        <v>-205.226708</v>
       </c>
       <c r="O61">
-        <v>-35.32757548799999</v>
+        <v>-49.25440992</v>
       </c>
       <c r="P61">
-        <v>-111.870655712</v>
+        <v>-155.97229808</v>
       </c>
       <c r="Q61">
-        <v>-30.77065571199999</v>
+        <v>-74.87229808000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1507829756274595</v>
+        <v>0.154643867394089</v>
       </c>
       <c r="T61">
-        <v>2.158560475396939</v>
+        <v>2.237944473777836</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1217677890992817</v>
+        <v>0.1019654616212192</v>
       </c>
       <c r="W61">
-        <v>0.1763490279488643</v>
+        <v>0.2117565441497165</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5073657879136736</v>
+        <v>0.4248560900884134</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1889114734474655</v>
+        <v>0.1908114734474655</v>
       </c>
       <c r="C62">
-        <v>-478.1872718795432</v>
+        <v>-512.7823890161083</v>
       </c>
       <c r="D62">
-        <v>741.0727281204566</v>
+        <v>731.6986109838916</v>
       </c>
       <c r="E62">
-        <v>1037.96</v>
+        <v>1063.181</v>
       </c>
       <c r="F62">
-        <v>1513.26</v>
+        <v>1538.481</v>
       </c>
       <c r="G62">
         <v>294</v>
@@ -6377,37 +6377,37 @@
         <v>151.6</v>
       </c>
       <c r="M62">
-        <v>356.826708</v>
+        <v>362.7738198</v>
       </c>
       <c r="N62">
-        <v>-205.226708</v>
+        <v>-211.1738198</v>
       </c>
       <c r="O62">
-        <v>-49.25440992</v>
+        <v>-50.681716752</v>
       </c>
       <c r="P62">
-        <v>-155.97229808</v>
+        <v>-160.492103048</v>
       </c>
       <c r="Q62">
-        <v>-74.87229808000001</v>
+        <v>-79.39210304800002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.154643867394089</v>
+        <v>0.1574347357888093</v>
       </c>
       <c r="T62">
-        <v>2.237944473777836</v>
+        <v>2.295327665413165</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1019654616212192</v>
+        <v>0.1002938966766091</v>
       </c>
       <c r="W62">
-        <v>0.2117565441497165</v>
+        <v>0.2121506991636556</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4248560900884134</v>
+        <v>0.4178912361525378</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1908114734474655</v>
+        <v>0.1927114734474655</v>
       </c>
       <c r="C63">
-        <v>-512.7823890161083</v>
+        <v>-547.14331482348</v>
       </c>
       <c r="D63">
-        <v>731.6986109838916</v>
+        <v>722.55868517652</v>
       </c>
       <c r="E63">
-        <v>1063.181</v>
+        <v>1088.402</v>
       </c>
       <c r="F63">
-        <v>1538.481</v>
+        <v>1563.702</v>
       </c>
       <c r="G63">
         <v>294</v>
@@ -6459,37 +6459,37 @@
         <v>151.6</v>
       </c>
       <c r="M63">
-        <v>362.7738198</v>
+        <v>368.7209316</v>
       </c>
       <c r="N63">
-        <v>-211.1738198</v>
+        <v>-217.1209316</v>
       </c>
       <c r="O63">
-        <v>-50.681716752</v>
+        <v>-52.10902358400001</v>
       </c>
       <c r="P63">
-        <v>-160.492103048</v>
+        <v>-165.011908016</v>
       </c>
       <c r="Q63">
-        <v>-79.39210304800002</v>
+        <v>-83.91190801600004</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1574347357888093</v>
+        <v>0.1603724919937779</v>
       </c>
       <c r="T63">
-        <v>2.295327665413165</v>
+        <v>2.355731025029301</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1002938966766091</v>
+        <v>0.09867625318182503</v>
       </c>
       <c r="W63">
-        <v>0.2121506991636556</v>
+        <v>0.2125321394997257</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4178912361525378</v>
+        <v>0.4111510549242711</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1927114734474655</v>
+        <v>0.1946114734474655</v>
       </c>
       <c r="C64">
-        <v>-547.14331482348</v>
+        <v>-581.2787171473515</v>
       </c>
       <c r="D64">
-        <v>722.55868517652</v>
+        <v>713.6442828526485</v>
       </c>
       <c r="E64">
-        <v>1088.402</v>
+        <v>1113.623</v>
       </c>
       <c r="F64">
-        <v>1563.702</v>
+        <v>1588.923</v>
       </c>
       <c r="G64">
         <v>294</v>
@@ -6541,37 +6541,37 @@
         <v>151.6</v>
       </c>
       <c r="M64">
-        <v>368.7209316</v>
+        <v>374.6680434</v>
       </c>
       <c r="N64">
-        <v>-217.1209316</v>
+        <v>-223.0680434</v>
       </c>
       <c r="O64">
-        <v>-52.10902358400001</v>
+        <v>-53.536330416</v>
       </c>
       <c r="P64">
-        <v>-165.011908016</v>
+        <v>-169.531712984</v>
       </c>
       <c r="Q64">
-        <v>-83.91190801600004</v>
+        <v>-88.431712984</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1603724919937779</v>
+        <v>0.1634690458314476</v>
       </c>
       <c r="T64">
-        <v>2.355731025029301</v>
+        <v>2.419399431111174</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09867625318182503</v>
+        <v>0.09710996344878021</v>
       </c>
       <c r="W64">
-        <v>0.2125321394997257</v>
+        <v>0.2129014706187776</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4111510549242711</v>
+        <v>0.4046248477032509</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1946114734474655</v>
+        <v>0.1965114734474655</v>
       </c>
       <c r="C65">
-        <v>-581.2787171473515</v>
+        <v>-615.196841296127</v>
       </c>
       <c r="D65">
-        <v>713.6442828526485</v>
+        <v>704.947158703873</v>
       </c>
       <c r="E65">
-        <v>1113.623</v>
+        <v>1138.844</v>
       </c>
       <c r="F65">
-        <v>1588.923</v>
+        <v>1614.144</v>
       </c>
       <c r="G65">
         <v>294</v>
@@ -6623,37 +6623,37 @@
         <v>151.6</v>
       </c>
       <c r="M65">
-        <v>374.6680434</v>
+        <v>380.6151552</v>
       </c>
       <c r="N65">
-        <v>-223.0680434</v>
+        <v>-229.0151552</v>
       </c>
       <c r="O65">
-        <v>-53.536330416</v>
+        <v>-54.963637248</v>
       </c>
       <c r="P65">
-        <v>-169.531712984</v>
+        <v>-174.051517952</v>
       </c>
       <c r="Q65">
-        <v>-88.431712984</v>
+        <v>-92.95151795200002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1634690458314476</v>
+        <v>0.1667376304378767</v>
       </c>
       <c r="T65">
-        <v>2.419399431111174</v>
+        <v>2.486604970864263</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09710996344878021</v>
+        <v>0.09559262026989301</v>
       </c>
       <c r="W65">
-        <v>0.2129014706187776</v>
+        <v>0.2132592601403592</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4046248477032509</v>
+        <v>0.3983025844578876</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1965114734474655</v>
+        <v>0.1984114734474655</v>
       </c>
       <c r="C66">
-        <v>-615.196841296127</v>
+        <v>-648.905535478058</v>
       </c>
       <c r="D66">
-        <v>704.947158703873</v>
+        <v>696.459464521942</v>
       </c>
       <c r="E66">
-        <v>1138.844</v>
+        <v>1164.065</v>
       </c>
       <c r="F66">
-        <v>1614.144</v>
+        <v>1639.365</v>
       </c>
       <c r="G66">
         <v>294</v>
@@ -6705,37 +6705,37 @@
         <v>151.6</v>
       </c>
       <c r="M66">
-        <v>380.6151552</v>
+        <v>386.562267</v>
       </c>
       <c r="N66">
-        <v>-229.0151552</v>
+        <v>-234.962267</v>
       </c>
       <c r="O66">
-        <v>-54.963637248</v>
+        <v>-56.39094408</v>
       </c>
       <c r="P66">
-        <v>-174.051517952</v>
+        <v>-178.57132292</v>
       </c>
       <c r="Q66">
-        <v>-92.95151795200002</v>
+        <v>-97.47132292000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1667376304378767</v>
+        <v>0.1701929913075304</v>
       </c>
       <c r="T66">
-        <v>2.486604970864263</v>
+        <v>2.55765082717467</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09559262026989301</v>
+        <v>0.09412196457343311</v>
       </c>
       <c r="W66">
-        <v>0.2132592601403592</v>
+        <v>0.2136060407535845</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3983025844578876</v>
+        <v>0.3921748523893047</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1984114734474655</v>
+        <v>0.2003114734474656</v>
       </c>
       <c r="C67">
-        <v>-648.905535478058</v>
+        <v>-682.4122744226347</v>
       </c>
       <c r="D67">
-        <v>696.459464521942</v>
+        <v>688.1737255773653</v>
       </c>
       <c r="E67">
-        <v>1164.065</v>
+        <v>1189.286</v>
       </c>
       <c r="F67">
-        <v>1639.365</v>
+        <v>1664.586</v>
       </c>
       <c r="G67">
         <v>294</v>
@@ -6787,37 +6787,37 @@
         <v>151.6</v>
       </c>
       <c r="M67">
-        <v>386.562267</v>
+        <v>392.5093788</v>
       </c>
       <c r="N67">
-        <v>-234.962267</v>
+        <v>-240.9093788</v>
       </c>
       <c r="O67">
-        <v>-56.39094408</v>
+        <v>-57.81825091200001</v>
       </c>
       <c r="P67">
-        <v>-178.57132292</v>
+        <v>-183.091127888</v>
       </c>
       <c r="Q67">
-        <v>-97.47132292000003</v>
+        <v>-101.991127888</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1701929913075304</v>
+        <v>0.1738516086989283</v>
       </c>
       <c r="T67">
-        <v>2.55765082717467</v>
+        <v>2.632875851503337</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09412196457343311</v>
+        <v>0.09269587420110836</v>
       </c>
       <c r="W67">
-        <v>0.2136060407535845</v>
+        <v>0.2139423128633787</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3921748523893047</v>
+        <v>0.3862328091712849</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2003114734474656</v>
+        <v>0.2022114734474655</v>
       </c>
       <c r="C68">
-        <v>-682.4122744226347</v>
+        <v>-715.7241813356624</v>
       </c>
       <c r="D68">
-        <v>688.1737255773653</v>
+        <v>680.0828186643377</v>
       </c>
       <c r="E68">
-        <v>1189.286</v>
+        <v>1214.507</v>
       </c>
       <c r="F68">
-        <v>1664.586</v>
+        <v>1689.807</v>
       </c>
       <c r="G68">
         <v>294</v>
@@ -6869,37 +6869,37 @@
         <v>151.6</v>
       </c>
       <c r="M68">
-        <v>392.5093788</v>
+        <v>398.4564906</v>
       </c>
       <c r="N68">
-        <v>-240.9093788</v>
+        <v>-246.8564906</v>
       </c>
       <c r="O68">
-        <v>-57.81825091200001</v>
+        <v>-59.245557744</v>
       </c>
       <c r="P68">
-        <v>-183.091127888</v>
+        <v>-187.610932856</v>
       </c>
       <c r="Q68">
-        <v>-101.991127888</v>
+        <v>-106.510932856</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1738516086989283</v>
+        <v>0.1777319604776837</v>
       </c>
       <c r="T68">
-        <v>2.632875851503337</v>
+        <v>2.712659968215559</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09269587420110836</v>
+        <v>0.09131235369064408</v>
       </c>
       <c r="W68">
-        <v>0.2139423128633787</v>
+        <v>0.2142685469997462</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3862328091712849</v>
+        <v>0.3804681403776837</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2022114734474655</v>
+        <v>0.2041114734474656</v>
       </c>
       <c r="C69">
-        <v>-715.7241813356624</v>
+        <v>-748.8480483235797</v>
       </c>
       <c r="D69">
-        <v>680.0828186643377</v>
+        <v>672.1799516764203</v>
       </c>
       <c r="E69">
-        <v>1214.507</v>
+        <v>1239.728</v>
       </c>
       <c r="F69">
-        <v>1689.807</v>
+        <v>1715.028</v>
       </c>
       <c r="G69">
         <v>294</v>
@@ -6951,37 +6951,37 @@
         <v>151.6</v>
       </c>
       <c r="M69">
-        <v>398.4564906</v>
+        <v>404.4036024</v>
       </c>
       <c r="N69">
-        <v>-246.8564906</v>
+        <v>-252.8036024</v>
       </c>
       <c r="O69">
-        <v>-59.245557744</v>
+        <v>-60.672864576</v>
       </c>
       <c r="P69">
-        <v>-187.610932856</v>
+        <v>-192.130737824</v>
       </c>
       <c r="Q69">
-        <v>-106.510932856</v>
+        <v>-111.030737824</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1777319604776837</v>
+        <v>0.1818548342426113</v>
       </c>
       <c r="T69">
-        <v>2.712659968215559</v>
+        <v>2.797430592222296</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09131235369064408</v>
+        <v>0.08996952495989931</v>
       </c>
       <c r="W69">
-        <v>0.2142685469997462</v>
+        <v>0.2145851860144558</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3804681403776837</v>
+        <v>0.3748730206662472</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2041114734474656</v>
+        <v>0.2060114734474655</v>
       </c>
       <c r="C70">
-        <v>-748.8480483235797</v>
+        <v>-781.7903554100889</v>
       </c>
       <c r="D70">
-        <v>672.1799516764203</v>
+        <v>664.4586445899112</v>
       </c>
       <c r="E70">
-        <v>1239.728</v>
+        <v>1264.949</v>
       </c>
       <c r="F70">
-        <v>1715.028</v>
+        <v>1740.249</v>
       </c>
       <c r="G70">
         <v>294</v>
@@ -7033,37 +7033,37 @@
         <v>151.6</v>
       </c>
       <c r="M70">
-        <v>404.4036024</v>
+        <v>410.3507142</v>
       </c>
       <c r="N70">
-        <v>-252.8036024</v>
+        <v>-258.7507142000001</v>
       </c>
       <c r="O70">
-        <v>-60.672864576</v>
+        <v>-62.10017140800002</v>
       </c>
       <c r="P70">
-        <v>-192.130737824</v>
+        <v>-196.650542792</v>
       </c>
       <c r="Q70">
-        <v>-111.030737824</v>
+        <v>-115.550542792</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1818548342426113</v>
+        <v>0.1862436998633407</v>
       </c>
       <c r="T70">
-        <v>2.797430592222296</v>
+        <v>2.887670288745595</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08996952495989931</v>
+        <v>0.08866561880106018</v>
       </c>
       <c r="W70">
-        <v>0.2145851860144558</v>
+        <v>0.21489264708671</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3748730206662472</v>
+        <v>0.3694400783377507</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2060114734474655</v>
+        <v>0.2079114734474656</v>
       </c>
       <c r="C71">
-        <v>-781.7903554100889</v>
+        <v>-814.5572882570131</v>
       </c>
       <c r="D71">
-        <v>664.4586445899112</v>
+        <v>656.912711742987</v>
       </c>
       <c r="E71">
-        <v>1264.949</v>
+        <v>1290.17</v>
       </c>
       <c r="F71">
-        <v>1740.249</v>
+        <v>1765.47</v>
       </c>
       <c r="G71">
         <v>294</v>
@@ -7115,37 +7115,37 @@
         <v>151.6</v>
       </c>
       <c r="M71">
-        <v>410.3507142</v>
+        <v>416.297826</v>
       </c>
       <c r="N71">
-        <v>-258.7507142000001</v>
+        <v>-264.6978260000001</v>
       </c>
       <c r="O71">
-        <v>-62.10017140800002</v>
+        <v>-63.52747824000001</v>
       </c>
       <c r="P71">
-        <v>-196.650542792</v>
+        <v>-201.1703477600001</v>
       </c>
       <c r="Q71">
-        <v>-115.550542792</v>
+        <v>-120.0703477600001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1862436998633407</v>
+        <v>0.1909251565254521</v>
       </c>
       <c r="T71">
-        <v>2.887670288745595</v>
+        <v>2.983925965037115</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08866561880106018</v>
+        <v>0.08739896710390217</v>
       </c>
       <c r="W71">
-        <v>0.21489264708671</v>
+        <v>0.2151913235568999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3694400783377507</v>
+        <v>0.3641623629329257</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2079114734474656</v>
+        <v>0.2098114734474655</v>
       </c>
       <c r="C72">
-        <v>-814.5572882570131</v>
+        <v>-847.1547546912303</v>
       </c>
       <c r="D72">
-        <v>656.912711742987</v>
+        <v>649.5362453087697</v>
       </c>
       <c r="E72">
-        <v>1290.17</v>
+        <v>1315.391</v>
       </c>
       <c r="F72">
-        <v>1765.47</v>
+        <v>1790.691</v>
       </c>
       <c r="G72">
         <v>294</v>
@@ -7197,37 +7197,37 @@
         <v>151.6</v>
       </c>
       <c r="M72">
-        <v>416.297826</v>
+        <v>422.2449378</v>
       </c>
       <c r="N72">
-        <v>-264.6978260000001</v>
+        <v>-270.6449378</v>
       </c>
       <c r="O72">
-        <v>-63.52747824000001</v>
+        <v>-64.95478507199999</v>
       </c>
       <c r="P72">
-        <v>-201.1703477600001</v>
+        <v>-205.690152728</v>
       </c>
       <c r="Q72">
-        <v>-120.0703477600001</v>
+        <v>-124.590152728</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1909251565254521</v>
+        <v>0.1959294722677091</v>
       </c>
       <c r="T72">
-        <v>2.983925965037115</v>
+        <v>3.086819963831499</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08739896710390217</v>
+        <v>0.08616799573624159</v>
       </c>
       <c r="W72">
-        <v>0.2151913235568999</v>
+        <v>0.2154815866053942</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3641623629329257</v>
+        <v>0.3590333155676734</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2098114734474655</v>
+        <v>0.2117114734474655</v>
       </c>
       <c r="C73">
-        <v>-847.1547546912301</v>
+        <v>-879.5884001304878</v>
       </c>
       <c r="D73">
-        <v>649.5362453087697</v>
+        <v>642.323599869512</v>
       </c>
       <c r="E73">
-        <v>1315.391</v>
+        <v>1340.612</v>
       </c>
       <c r="F73">
-        <v>1790.691</v>
+        <v>1815.912</v>
       </c>
       <c r="G73">
         <v>294</v>
@@ -7279,37 +7279,37 @@
         <v>151.6</v>
       </c>
       <c r="M73">
-        <v>422.2449377999999</v>
+        <v>428.1920496</v>
       </c>
       <c r="N73">
-        <v>-270.6449378</v>
+        <v>-276.5920496</v>
       </c>
       <c r="O73">
-        <v>-64.95478507199999</v>
+        <v>-66.38209190399999</v>
       </c>
       <c r="P73">
-        <v>-205.690152728</v>
+        <v>-210.209957696</v>
       </c>
       <c r="Q73">
-        <v>-124.590152728</v>
+        <v>-129.109957696</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.195929472267709</v>
+        <v>0.2012912391344129</v>
       </c>
       <c r="T73">
-        <v>3.086819963831498</v>
+        <v>3.197063533968337</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08616799573624161</v>
+        <v>0.08497121801768269</v>
       </c>
       <c r="W73">
-        <v>0.2154815866053942</v>
+        <v>0.2157637867914304</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3590333155676733</v>
+        <v>0.3540467417403445</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2117114734474655</v>
+        <v>0.2136114734474655</v>
       </c>
       <c r="C74">
-        <v>-879.5884001304878</v>
+        <v>-911.8636219927424</v>
       </c>
       <c r="D74">
-        <v>642.323599869512</v>
+        <v>635.2693780072574</v>
       </c>
       <c r="E74">
-        <v>1340.612</v>
+        <v>1365.833</v>
       </c>
       <c r="F74">
-        <v>1815.912</v>
+        <v>1841.133</v>
       </c>
       <c r="G74">
         <v>294</v>
@@ -7361,37 +7361,37 @@
         <v>151.6</v>
       </c>
       <c r="M74">
-        <v>428.1920496</v>
+        <v>434.1391614</v>
       </c>
       <c r="N74">
-        <v>-276.5920496</v>
+        <v>-282.5391614</v>
       </c>
       <c r="O74">
-        <v>-66.38209190399999</v>
+        <v>-67.80939873600001</v>
       </c>
       <c r="P74">
-        <v>-210.209957696</v>
+        <v>-214.729762664</v>
       </c>
       <c r="Q74">
-        <v>-129.109957696</v>
+        <v>-133.629762664</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2012912391344129</v>
+        <v>0.2070501739171689</v>
       </c>
       <c r="T74">
-        <v>3.197063533968337</v>
+        <v>3.315473294485682</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08497121801768269</v>
+        <v>0.08380722872976923</v>
       </c>
       <c r="W74">
-        <v>0.2157637867914304</v>
+        <v>0.2160382554655204</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3540467417403445</v>
+        <v>0.3491967863740384</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2136114734474655</v>
+        <v>0.2155114734474655</v>
       </c>
       <c r="C75">
-        <v>-911.8636219927424</v>
+        <v>-943.9855831663295</v>
       </c>
       <c r="D75">
-        <v>635.2693780072574</v>
+        <v>628.3684168336703</v>
       </c>
       <c r="E75">
-        <v>1365.833</v>
+        <v>1391.054</v>
       </c>
       <c r="F75">
-        <v>1841.133</v>
+        <v>1866.354</v>
       </c>
       <c r="G75">
         <v>294</v>
@@ -7443,37 +7443,37 @@
         <v>151.6</v>
       </c>
       <c r="M75">
-        <v>434.1391614</v>
+        <v>440.0862732</v>
       </c>
       <c r="N75">
-        <v>-282.5391614</v>
+        <v>-288.4862732</v>
       </c>
       <c r="O75">
-        <v>-67.80939873600001</v>
+        <v>-69.236705568</v>
       </c>
       <c r="P75">
-        <v>-214.729762664</v>
+        <v>-219.249567632</v>
       </c>
       <c r="Q75">
-        <v>-133.629762664</v>
+        <v>-138.149567632</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2070501739171689</v>
+        <v>0.2132521036832139</v>
       </c>
       <c r="T75">
-        <v>3.315473294485682</v>
+        <v>3.442991498119747</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08380722872976923</v>
+        <v>0.08267469861179938</v>
       </c>
       <c r="W75">
-        <v>0.2160382554655204</v>
+        <v>0.2163053060673377</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3491967863740384</v>
+        <v>0.3444779108824974</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2155114734474655</v>
+        <v>0.2174114734474655</v>
       </c>
       <c r="C76">
-        <v>-943.9855831663295</v>
+        <v>-975.9592246116032</v>
       </c>
       <c r="D76">
-        <v>628.3684168336703</v>
+        <v>621.6157753883966</v>
       </c>
       <c r="E76">
-        <v>1391.054</v>
+        <v>1416.275</v>
       </c>
       <c r="F76">
-        <v>1866.354</v>
+        <v>1891.575</v>
       </c>
       <c r="G76">
         <v>294</v>
@@ -7525,37 +7525,37 @@
         <v>151.6</v>
       </c>
       <c r="M76">
-        <v>440.0862732</v>
+        <v>446.033385</v>
       </c>
       <c r="N76">
-        <v>-288.4862732</v>
+        <v>-294.4333849999999</v>
       </c>
       <c r="O76">
-        <v>-69.236705568</v>
+        <v>-70.66401239999998</v>
       </c>
       <c r="P76">
-        <v>-219.249567632</v>
+        <v>-223.7693725999999</v>
       </c>
       <c r="Q76">
-        <v>-138.149567632</v>
+        <v>-142.6693725999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2132521036832139</v>
+        <v>0.2199501878305425</v>
       </c>
       <c r="T76">
-        <v>3.442991498119747</v>
+        <v>3.580711158044537</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08267469861179938</v>
+        <v>0.08157236929697538</v>
       </c>
       <c r="W76">
-        <v>0.2163053060673377</v>
+        <v>0.2165652353197732</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3444779108824974</v>
+        <v>0.3398848720707308</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2174114734474655</v>
+        <v>0.2193114734474655</v>
       </c>
       <c r="C77">
-        <v>-975.9592246116032</v>
+        <v>-1007.789277158684</v>
       </c>
       <c r="D77">
-        <v>621.6157753883966</v>
+        <v>615.0067228413159</v>
       </c>
       <c r="E77">
-        <v>1416.275</v>
+        <v>1441.496</v>
       </c>
       <c r="F77">
-        <v>1891.575</v>
+        <v>1916.796</v>
       </c>
       <c r="G77">
         <v>294</v>
@@ -7607,37 +7607,37 @@
         <v>151.6</v>
       </c>
       <c r="M77">
-        <v>446.033385</v>
+        <v>451.9804968</v>
       </c>
       <c r="N77">
-        <v>-294.4333849999999</v>
+        <v>-300.3804968000001</v>
       </c>
       <c r="O77">
-        <v>-70.66401239999998</v>
+        <v>-72.09131923200002</v>
       </c>
       <c r="P77">
-        <v>-223.7693725999999</v>
+        <v>-228.289177568</v>
       </c>
       <c r="Q77">
-        <v>-142.6693725999999</v>
+        <v>-147.189177568</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2199501878305425</v>
+        <v>0.2272064456568151</v>
       </c>
       <c r="T77">
-        <v>3.580711158044537</v>
+        <v>3.729907456296393</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08157236929697538</v>
+        <v>0.08049904864833096</v>
       </c>
       <c r="W77">
-        <v>0.2165652353197732</v>
+        <v>0.2168183243287236</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3398848720707308</v>
+        <v>0.3354127027013789</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2193114734474655</v>
+        <v>0.2212114734474655</v>
       </c>
       <c r="C78">
-        <v>-1007.789277158684</v>
+        <v>-1039.480272560528</v>
       </c>
       <c r="D78">
-        <v>615.0067228413159</v>
+        <v>608.536727439472</v>
       </c>
       <c r="E78">
-        <v>1441.496</v>
+        <v>1466.717</v>
       </c>
       <c r="F78">
-        <v>1916.796</v>
+        <v>1942.017</v>
       </c>
       <c r="G78">
         <v>294</v>
@@ -7689,37 +7689,37 @@
         <v>151.6</v>
       </c>
       <c r="M78">
-        <v>451.9804968</v>
+        <v>457.9276086</v>
       </c>
       <c r="N78">
-        <v>-300.3804968000001</v>
+        <v>-306.3276086000001</v>
       </c>
       <c r="O78">
-        <v>-72.09131923200002</v>
+        <v>-73.51862606400002</v>
       </c>
       <c r="P78">
-        <v>-228.289177568</v>
+        <v>-232.8089825360001</v>
       </c>
       <c r="Q78">
-        <v>-147.189177568</v>
+        <v>-151.7089825360001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2272064456568151</v>
+        <v>0.2350936824245027</v>
       </c>
       <c r="T78">
-        <v>3.729907456296393</v>
+        <v>3.892077345700585</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08049904864833096</v>
+        <v>0.07945360645809289</v>
       </c>
       <c r="W78">
-        <v>0.2168183243287236</v>
+        <v>0.2170648395971817</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3354127027013789</v>
+        <v>0.331056693575387</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2212114734474655</v>
+        <v>0.2231114734474655</v>
       </c>
       <c r="C79">
-        <v>-1039.480272560528</v>
+        <v>-1071.036553855564</v>
       </c>
       <c r="D79">
-        <v>608.536727439472</v>
+        <v>602.2014461444361</v>
       </c>
       <c r="E79">
-        <v>1466.717</v>
+        <v>1491.938</v>
       </c>
       <c r="F79">
-        <v>1942.017</v>
+        <v>1967.238</v>
       </c>
       <c r="G79">
         <v>294</v>
@@ -7771,37 +7771,37 @@
         <v>151.6</v>
       </c>
       <c r="M79">
-        <v>457.9276086</v>
+        <v>463.8747204000001</v>
       </c>
       <c r="N79">
-        <v>-306.3276086000001</v>
+        <v>-312.2747204000001</v>
       </c>
       <c r="O79">
-        <v>-73.51862606400002</v>
+        <v>-74.94593289600002</v>
       </c>
       <c r="P79">
-        <v>-232.8089825360001</v>
+        <v>-237.3287875040001</v>
       </c>
       <c r="Q79">
-        <v>-151.7089825360001</v>
+        <v>-156.2287875040001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2350936824245027</v>
+        <v>0.2436979407165255</v>
       </c>
       <c r="T79">
-        <v>3.892077345700585</v>
+        <v>4.068989952323338</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07945360645809289</v>
+        <v>0.07843497047786094</v>
       </c>
       <c r="W79">
-        <v>0.2170648395971817</v>
+        <v>0.2173050339613204</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.331056693575387</v>
+        <v>0.3268123769910871</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2231114734474655</v>
+        <v>0.2250114734474656</v>
       </c>
       <c r="C80">
-        <v>-1071.036553855564</v>
+        <v>-1102.462285089719</v>
       </c>
       <c r="D80">
-        <v>602.2014461444361</v>
+        <v>595.996714910281</v>
       </c>
       <c r="E80">
-        <v>1491.938</v>
+        <v>1517.159</v>
       </c>
       <c r="F80">
-        <v>1967.238</v>
+        <v>1992.459</v>
       </c>
       <c r="G80">
         <v>294</v>
@@ -7853,37 +7853,37 @@
         <v>151.6</v>
       </c>
       <c r="M80">
-        <v>463.8747204000001</v>
+        <v>469.8218322</v>
       </c>
       <c r="N80">
-        <v>-312.2747204000001</v>
+        <v>-318.2218322</v>
       </c>
       <c r="O80">
-        <v>-74.94593289600002</v>
+        <v>-76.373239728</v>
       </c>
       <c r="P80">
-        <v>-237.3287875040001</v>
+        <v>-241.848592472</v>
       </c>
       <c r="Q80">
-        <v>-156.2287875040001</v>
+        <v>-160.748592472</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2436979407165255</v>
+        <v>0.2531216521792172</v>
       </c>
       <c r="T80">
-        <v>4.068989952323338</v>
+        <v>4.262751378624451</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07843497047786094</v>
+        <v>0.07744212275029307</v>
       </c>
       <c r="W80">
-        <v>0.2173050339613204</v>
+        <v>0.2175391474554809</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3268123769910871</v>
+        <v>0.3226755114595545</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2250114734474656</v>
+        <v>0.2269114734474655</v>
       </c>
       <c r="C81">
-        <v>-1102.462285089719</v>
+        <v>-1133.761460443544</v>
       </c>
       <c r="D81">
-        <v>595.996714910281</v>
+        <v>589.9185395564562</v>
       </c>
       <c r="E81">
-        <v>1517.159</v>
+        <v>1542.38</v>
       </c>
       <c r="F81">
-        <v>1992.459</v>
+        <v>2017.68</v>
       </c>
       <c r="G81">
         <v>294</v>
@@ -7935,37 +7935,37 @@
         <v>151.6</v>
       </c>
       <c r="M81">
-        <v>469.8218322</v>
+        <v>475.768944</v>
       </c>
       <c r="N81">
-        <v>-318.2218322</v>
+        <v>-324.168944</v>
       </c>
       <c r="O81">
-        <v>-76.373239728</v>
+        <v>-77.80054656</v>
       </c>
       <c r="P81">
-        <v>-241.848592472</v>
+        <v>-246.36839744</v>
       </c>
       <c r="Q81">
-        <v>-160.748592472</v>
+        <v>-165.26839744</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2531216521792172</v>
+        <v>0.2634877347881781</v>
       </c>
       <c r="T81">
-        <v>4.262751378624451</v>
+        <v>4.475888947555673</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07744212275029307</v>
+        <v>0.0764740962159144</v>
       </c>
       <c r="W81">
-        <v>0.2175391474554809</v>
+        <v>0.2177674081122874</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3226755114595545</v>
+        <v>0.3186420675663101</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2269114734474655</v>
+        <v>0.2288114734474655</v>
       </c>
       <c r="C82">
-        <v>-1133.761460443544</v>
+        <v>-1164.937912806495</v>
       </c>
       <c r="D82">
-        <v>589.9185395564562</v>
+        <v>583.9630871935054</v>
       </c>
       <c r="E82">
-        <v>1542.38</v>
+        <v>1567.601</v>
       </c>
       <c r="F82">
-        <v>2017.68</v>
+        <v>2042.901</v>
       </c>
       <c r="G82">
         <v>294</v>
@@ -8017,37 +8017,37 @@
         <v>151.6</v>
       </c>
       <c r="M82">
-        <v>475.768944</v>
+        <v>481.7160558</v>
       </c>
       <c r="N82">
-        <v>-324.168944</v>
+        <v>-330.1160558</v>
       </c>
       <c r="O82">
-        <v>-77.80054656</v>
+        <v>-79.227853392</v>
       </c>
       <c r="P82">
-        <v>-246.36839744</v>
+        <v>-250.888202408</v>
       </c>
       <c r="Q82">
-        <v>-165.26839744</v>
+        <v>-169.788202408</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2634877347881781</v>
+        <v>0.2749449839875559</v>
       </c>
       <c r="T82">
-        <v>4.475888947555673</v>
+        <v>4.711462050058603</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0764740962159144</v>
+        <v>0.07552997157127349</v>
       </c>
       <c r="W82">
-        <v>0.2177674081122874</v>
+        <v>0.2179900327034937</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3186420675663101</v>
+        <v>0.3147082148803063</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2288114734474655</v>
+        <v>0.2307114734474655</v>
       </c>
       <c r="C83">
-        <v>-1164.937912806495</v>
+        <v>-1195.995321837035</v>
       </c>
       <c r="D83">
-        <v>583.9630871935054</v>
+        <v>578.1266781629654</v>
       </c>
       <c r="E83">
-        <v>1567.601</v>
+        <v>1592.822</v>
       </c>
       <c r="F83">
-        <v>2042.901</v>
+        <v>2068.122</v>
       </c>
       <c r="G83">
         <v>294</v>
@@ -8099,37 +8099,37 @@
         <v>151.6</v>
       </c>
       <c r="M83">
-        <v>481.7160558</v>
+        <v>487.6631676000001</v>
       </c>
       <c r="N83">
-        <v>-330.1160558</v>
+        <v>-336.0631676</v>
       </c>
       <c r="O83">
-        <v>-79.227853392</v>
+        <v>-80.65516022400001</v>
       </c>
       <c r="P83">
-        <v>-250.888202408</v>
+        <v>-255.408007376</v>
       </c>
       <c r="Q83">
-        <v>-169.788202408</v>
+        <v>-174.308007376</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2749449839875559</v>
+        <v>0.2876752608757535</v>
       </c>
       <c r="T83">
-        <v>4.711462050058603</v>
+        <v>4.973209941728525</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07552997157127349</v>
+        <v>0.07460887435698967</v>
       </c>
       <c r="W83">
-        <v>0.2179900327034937</v>
+        <v>0.2182072274266218</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3147082148803063</v>
+        <v>0.3108703098207903</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2307114734474655</v>
+        <v>0.2326114734474655</v>
       </c>
       <c r="C84">
-        <v>-1195.995321837035</v>
+        <v>-1226.937221544187</v>
       </c>
       <c r="D84">
-        <v>578.1266781629654</v>
+        <v>572.4057784558133</v>
       </c>
       <c r="E84">
-        <v>1592.822</v>
+        <v>1618.043</v>
       </c>
       <c r="F84">
-        <v>2068.122</v>
+        <v>2093.343</v>
       </c>
       <c r="G84">
         <v>294</v>
@@ -8181,37 +8181,37 @@
         <v>151.6</v>
       </c>
       <c r="M84">
-        <v>487.6631676000001</v>
+        <v>493.6102794000001</v>
       </c>
       <c r="N84">
-        <v>-336.0631676</v>
+        <v>-342.0102794000001</v>
       </c>
       <c r="O84">
-        <v>-80.65516022400001</v>
+        <v>-82.08246705600001</v>
       </c>
       <c r="P84">
-        <v>-255.408007376</v>
+        <v>-259.927812344</v>
       </c>
       <c r="Q84">
-        <v>-174.308007376</v>
+        <v>-178.827812344</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2876752608757535</v>
+        <v>0.3019032173978566</v>
       </c>
       <c r="T84">
-        <v>4.973209941728525</v>
+        <v>5.265751703006675</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07460887435698967</v>
+        <v>0.07370997225630303</v>
       </c>
       <c r="W84">
-        <v>0.2182072274266218</v>
+        <v>0.2184191885419637</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3108703098207903</v>
+        <v>0.3071248844012627</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2326114734474655</v>
+        <v>0.2345114734474656</v>
       </c>
       <c r="C85">
-        <v>-1226.937221544187</v>
+        <v>-1257.767007423348</v>
       </c>
       <c r="D85">
-        <v>572.4057784558133</v>
+        <v>566.7969925766525</v>
       </c>
       <c r="E85">
-        <v>1618.043</v>
+        <v>1643.264</v>
       </c>
       <c r="F85">
-        <v>2093.343</v>
+        <v>2118.564</v>
       </c>
       <c r="G85">
         <v>294</v>
@@ -8263,37 +8263,37 @@
         <v>151.6</v>
       </c>
       <c r="M85">
-        <v>493.6102794000001</v>
+        <v>499.5573912000001</v>
       </c>
       <c r="N85">
-        <v>-342.0102794000001</v>
+        <v>-347.9573912000001</v>
       </c>
       <c r="O85">
-        <v>-82.08246705600001</v>
+        <v>-83.50977388800001</v>
       </c>
       <c r="P85">
-        <v>-259.927812344</v>
+        <v>-264.447617312</v>
       </c>
       <c r="Q85">
-        <v>-178.827812344</v>
+        <v>-183.347617312</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3019032173978566</v>
+        <v>0.3179096684852228</v>
       </c>
       <c r="T85">
-        <v>5.265751703006675</v>
+        <v>5.594861184444594</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07370997225630303</v>
+        <v>0.07283247258658514</v>
       </c>
       <c r="W85">
-        <v>0.2184191885419637</v>
+        <v>0.2186261029640832</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3071248844012627</v>
+        <v>0.3034686357774382</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2345114734474655</v>
+        <v>0.2364114734474655</v>
       </c>
       <c r="C86">
-        <v>-1257.767007423347</v>
+        <v>-1288.487943176648</v>
       </c>
       <c r="D86">
-        <v>566.7969925766528</v>
+        <v>561.2970568233519</v>
       </c>
       <c r="E86">
-        <v>1643.264</v>
+        <v>1668.485</v>
       </c>
       <c r="F86">
-        <v>2118.564</v>
+        <v>2143.785</v>
       </c>
       <c r="G86">
         <v>294</v>
@@ -8345,37 +8345,37 @@
         <v>151.6</v>
       </c>
       <c r="M86">
-        <v>499.5573912</v>
+        <v>505.504503</v>
       </c>
       <c r="N86">
-        <v>-347.9573912</v>
+        <v>-353.904503</v>
       </c>
       <c r="O86">
-        <v>-83.50977388799998</v>
+        <v>-84.93708072</v>
       </c>
       <c r="P86">
-        <v>-264.447617312</v>
+        <v>-268.96742228</v>
       </c>
       <c r="Q86">
-        <v>-183.347617312</v>
+        <v>-187.86742228</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3179096684852225</v>
+        <v>0.336050313050904</v>
       </c>
       <c r="T86">
-        <v>5.594861184444588</v>
+        <v>5.967851930074229</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07283247258658515</v>
+        <v>0.07197561996791944</v>
       </c>
       <c r="W86">
-        <v>0.2186261029640832</v>
+        <v>0.2188281488115646</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3034686357774382</v>
+        <v>0.2998984165329978</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2364114734474655</v>
+        <v>0.2383114734474655</v>
       </c>
       <c r="C87">
-        <v>-1288.487943176648</v>
+        <v>-1319.103167045809</v>
       </c>
       <c r="D87">
-        <v>561.2970568233519</v>
+        <v>555.9028329541906</v>
       </c>
       <c r="E87">
-        <v>1668.485</v>
+        <v>1693.706</v>
       </c>
       <c r="F87">
-        <v>2143.785</v>
+        <v>2169.006</v>
       </c>
       <c r="G87">
         <v>294</v>
@@ -8427,37 +8427,37 @@
         <v>151.6</v>
       </c>
       <c r="M87">
-        <v>505.504503</v>
+        <v>511.4516148</v>
       </c>
       <c r="N87">
-        <v>-353.904503</v>
+        <v>-359.8516148</v>
       </c>
       <c r="O87">
-        <v>-84.93708072</v>
+        <v>-86.364387552</v>
       </c>
       <c r="P87">
-        <v>-268.96742228</v>
+        <v>-273.487227248</v>
       </c>
       <c r="Q87">
-        <v>-187.86742228</v>
+        <v>-192.387227248</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.336050313050904</v>
+        <v>0.3567824782688258</v>
       </c>
       <c r="T87">
-        <v>5.967851930074229</v>
+        <v>6.394127067936673</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07197561996791944</v>
+        <v>0.07113869415433899</v>
       </c>
       <c r="W87">
-        <v>0.2188281488115646</v>
+        <v>0.2190254959184069</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2998984165329978</v>
+        <v>0.2964112256430792</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2383114734474655</v>
+        <v>0.2402114734474655</v>
       </c>
       <c r="C88">
-        <v>-1319.103167045809</v>
+        <v>-1349.615697783307</v>
       </c>
       <c r="D88">
-        <v>555.9028329541906</v>
+        <v>550.6113022166934</v>
       </c>
       <c r="E88">
-        <v>1693.706</v>
+        <v>1718.927</v>
       </c>
       <c r="F88">
-        <v>2169.006</v>
+        <v>2194.227</v>
       </c>
       <c r="G88">
         <v>294</v>
@@ -8509,37 +8509,37 @@
         <v>151.6</v>
       </c>
       <c r="M88">
-        <v>511.4516148</v>
+        <v>517.3987266</v>
       </c>
       <c r="N88">
-        <v>-359.8516148</v>
+        <v>-365.7987266</v>
       </c>
       <c r="O88">
-        <v>-86.364387552</v>
+        <v>-87.791694384</v>
       </c>
       <c r="P88">
-        <v>-273.487227248</v>
+        <v>-278.007032216</v>
       </c>
       <c r="Q88">
-        <v>-192.387227248</v>
+        <v>-196.907032216</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3567824782688258</v>
+        <v>0.3807042073664278</v>
       </c>
       <c r="T88">
-        <v>6.394127067936673</v>
+        <v>6.885982996239495</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07113869415433899</v>
+        <v>0.07032100801463394</v>
       </c>
       <c r="W88">
-        <v>0.2190254959184069</v>
+        <v>0.2192183063101493</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2964112256430792</v>
+        <v>0.2930042000609748</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2402114734474655</v>
+        <v>0.2421114734474655</v>
       </c>
       <c r="C89">
-        <v>-1349.615697783307</v>
+        <v>-1380.02844028572</v>
       </c>
       <c r="D89">
-        <v>550.6113022166934</v>
+        <v>545.4195597142801</v>
       </c>
       <c r="E89">
-        <v>1718.927</v>
+        <v>1744.148</v>
       </c>
       <c r="F89">
-        <v>2194.227</v>
+        <v>2219.448</v>
       </c>
       <c r="G89">
         <v>294</v>
@@ -8591,37 +8591,37 @@
         <v>151.6</v>
       </c>
       <c r="M89">
-        <v>517.3987266</v>
+        <v>523.3458383999999</v>
       </c>
       <c r="N89">
-        <v>-365.7987266</v>
+        <v>-371.7458383999999</v>
       </c>
       <c r="O89">
-        <v>-87.791694384</v>
+        <v>-89.21900121599998</v>
       </c>
       <c r="P89">
-        <v>-278.007032216</v>
+        <v>-282.5268371839999</v>
       </c>
       <c r="Q89">
-        <v>-196.907032216</v>
+        <v>-201.4268371839999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3807042073664278</v>
+        <v>0.4086128913136301</v>
       </c>
       <c r="T89">
-        <v>6.885982996239495</v>
+        <v>7.459814912592787</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07032100801463394</v>
+        <v>0.0695219056508313</v>
       </c>
       <c r="W89">
-        <v>0.2192183063101493</v>
+        <v>0.219406734647534</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2930042000609748</v>
+        <v>0.2896746068784638</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2421114734474655</v>
+        <v>0.2440114734474655</v>
       </c>
       <c r="C90">
-        <v>-1380.02844028572</v>
+        <v>-1410.344190911362</v>
       </c>
       <c r="D90">
-        <v>545.4195597142801</v>
+        <v>540.3248090886383</v>
       </c>
       <c r="E90">
-        <v>1744.148</v>
+        <v>1769.369</v>
       </c>
       <c r="F90">
-        <v>2219.448</v>
+        <v>2244.669</v>
       </c>
       <c r="G90">
         <v>294</v>
@@ -8673,37 +8673,37 @@
         <v>151.6</v>
       </c>
       <c r="M90">
-        <v>523.3458383999999</v>
+        <v>529.2929502</v>
       </c>
       <c r="N90">
-        <v>-371.7458383999999</v>
+        <v>-377.6929501999999</v>
       </c>
       <c r="O90">
-        <v>-89.21900121599998</v>
+        <v>-90.64630804799998</v>
       </c>
       <c r="P90">
-        <v>-282.5268371839999</v>
+        <v>-287.0466421519999</v>
       </c>
       <c r="Q90">
-        <v>-201.4268371839999</v>
+        <v>-205.946642152</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4086128913136301</v>
+        <v>0.441595881433051</v>
       </c>
       <c r="T90">
-        <v>7.459814912592787</v>
+        <v>8.137979904646675</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0695219056508313</v>
+        <v>0.06874076064351858</v>
       </c>
       <c r="W90">
-        <v>0.219406734647534</v>
+        <v>0.2195909286402583</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2896746068784638</v>
+        <v>0.2864198360146608</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2440114734474655</v>
+        <v>0.2459114734474655</v>
       </c>
       <c r="C91">
-        <v>-1410.344190911362</v>
+        <v>-1440.565642502627</v>
       </c>
       <c r="D91">
-        <v>540.3248090886383</v>
+        <v>535.3243574973724</v>
       </c>
       <c r="E91">
-        <v>1769.369</v>
+        <v>1794.59</v>
       </c>
       <c r="F91">
-        <v>2244.669</v>
+        <v>2269.89</v>
       </c>
       <c r="G91">
         <v>294</v>
@@ -8755,37 +8755,37 @@
         <v>151.6</v>
       </c>
       <c r="M91">
-        <v>529.2929502</v>
+        <v>535.240062</v>
       </c>
       <c r="N91">
-        <v>-377.6929501999999</v>
+        <v>-383.6400619999999</v>
       </c>
       <c r="O91">
-        <v>-90.64630804799998</v>
+        <v>-92.07361487999998</v>
       </c>
       <c r="P91">
-        <v>-287.0466421519999</v>
+        <v>-291.56644712</v>
       </c>
       <c r="Q91">
-        <v>-205.946642152</v>
+        <v>-210.46644712</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.441595881433051</v>
+        <v>0.4811754695763562</v>
       </c>
       <c r="T91">
-        <v>8.137979904646675</v>
+        <v>8.951777895111345</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06874076064351858</v>
+        <v>0.06797697441414616</v>
       </c>
       <c r="W91">
-        <v>0.2195909286402583</v>
+        <v>0.2197710294331443</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2864198360146608</v>
+        <v>0.2832373933922757</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2459114734474655</v>
+        <v>0.2478114734474655</v>
       </c>
       <c r="C92">
-        <v>-1440.565642502627</v>
+        <v>-1470.695389132032</v>
       </c>
       <c r="D92">
-        <v>535.3243574973724</v>
+        <v>530.415610867968</v>
       </c>
       <c r="E92">
-        <v>1794.59</v>
+        <v>1819.811</v>
       </c>
       <c r="F92">
-        <v>2269.89</v>
+        <v>2295.111</v>
       </c>
       <c r="G92">
         <v>294</v>
@@ -8837,37 +8837,37 @@
         <v>151.6</v>
       </c>
       <c r="M92">
-        <v>535.240062</v>
+        <v>541.1871738</v>
       </c>
       <c r="N92">
-        <v>-383.6400619999999</v>
+        <v>-389.5871738</v>
       </c>
       <c r="O92">
-        <v>-92.07361487999998</v>
+        <v>-93.50092171199999</v>
       </c>
       <c r="P92">
-        <v>-291.56644712</v>
+        <v>-296.086252088</v>
       </c>
       <c r="Q92">
-        <v>-210.46644712</v>
+        <v>-214.986252088</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4811754695763562</v>
+        <v>0.5295505217515069</v>
       </c>
       <c r="T92">
-        <v>8.951777895111345</v>
+        <v>9.94641988345705</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06797697441414616</v>
+        <v>0.06722997469530938</v>
       </c>
       <c r="W92">
-        <v>0.2197710294331443</v>
+        <v>0.2199471719668461</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2832373933922757</v>
+        <v>0.2801248945637891</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2478114734474655</v>
+        <v>0.2497114734474655</v>
       </c>
       <c r="C93">
-        <v>-1470.695389132032</v>
+        <v>-1500.735930589492</v>
       </c>
       <c r="D93">
-        <v>530.415610867968</v>
+        <v>525.5960694105084</v>
       </c>
       <c r="E93">
-        <v>1819.811</v>
+        <v>1845.032</v>
       </c>
       <c r="F93">
-        <v>2295.111</v>
+        <v>2320.332</v>
       </c>
       <c r="G93">
         <v>294</v>
@@ -8919,37 +8919,37 @@
         <v>151.6</v>
       </c>
       <c r="M93">
-        <v>541.1871738</v>
+        <v>547.1342856</v>
       </c>
       <c r="N93">
-        <v>-389.5871738</v>
+        <v>-395.5342856</v>
       </c>
       <c r="O93">
-        <v>-93.50092171199999</v>
+        <v>-94.92822854399999</v>
       </c>
       <c r="P93">
-        <v>-296.086252088</v>
+        <v>-300.606057056</v>
       </c>
       <c r="Q93">
-        <v>-214.986252088</v>
+        <v>-219.506057056</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5295505217515069</v>
+        <v>0.5900193369704454</v>
       </c>
       <c r="T93">
-        <v>9.94641988345705</v>
+        <v>11.18972236888919</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06722997469530938</v>
+        <v>0.06649921410079514</v>
       </c>
       <c r="W93">
-        <v>0.2199471719668461</v>
+        <v>0.2201194853150325</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2801248945637891</v>
+        <v>0.2770800587533132</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2497114734474655</v>
+        <v>0.2516114734474655</v>
       </c>
       <c r="C94">
-        <v>-1500.735930589492</v>
+        <v>-1530.689676627184</v>
       </c>
       <c r="D94">
-        <v>525.5960694105084</v>
+        <v>520.8633233728157</v>
       </c>
       <c r="E94">
-        <v>1845.032</v>
+        <v>1870.253</v>
       </c>
       <c r="F94">
-        <v>2320.332</v>
+        <v>2345.553</v>
       </c>
       <c r="G94">
         <v>294</v>
@@ -9001,37 +9001,37 @@
         <v>151.6</v>
       </c>
       <c r="M94">
-        <v>547.1342856</v>
+        <v>553.0813974</v>
       </c>
       <c r="N94">
-        <v>-395.5342856</v>
+        <v>-401.4813974</v>
       </c>
       <c r="O94">
-        <v>-94.92822854399999</v>
+        <v>-96.35553537599999</v>
       </c>
       <c r="P94">
-        <v>-300.606057056</v>
+        <v>-305.125862024</v>
       </c>
       <c r="Q94">
-        <v>-219.506057056</v>
+        <v>-224.025862024</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5900193369704454</v>
+        <v>0.6677649565376519</v>
       </c>
       <c r="T94">
-        <v>11.18972236888919</v>
+        <v>12.78825413587336</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06649921410079514</v>
+        <v>0.06578416878788336</v>
       </c>
       <c r="W94">
-        <v>0.2201194853150325</v>
+        <v>0.2202880929998171</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2770800587533132</v>
+        <v>0.2741007032828474</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2516114734474655</v>
+        <v>0.2535114734474655</v>
       </c>
       <c r="C95">
-        <v>-1530.689676627184</v>
+        <v>-1560.558950977106</v>
       </c>
       <c r="D95">
-        <v>520.8633233728157</v>
+        <v>516.2150490228942</v>
       </c>
       <c r="E95">
-        <v>1870.253</v>
+        <v>1895.474</v>
       </c>
       <c r="F95">
-        <v>2345.553</v>
+        <v>2370.774</v>
       </c>
       <c r="G95">
         <v>294</v>
@@ -9083,37 +9083,37 @@
         <v>151.6</v>
       </c>
       <c r="M95">
-        <v>553.0813974</v>
+        <v>559.0285092</v>
       </c>
       <c r="N95">
-        <v>-401.4813974</v>
+        <v>-407.4285092</v>
       </c>
       <c r="O95">
-        <v>-96.35553537599999</v>
+        <v>-97.78284220800001</v>
       </c>
       <c r="P95">
-        <v>-305.125862024</v>
+        <v>-309.645666992</v>
       </c>
       <c r="Q95">
-        <v>-224.025862024</v>
+        <v>-228.545666992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6677649565376519</v>
+        <v>0.7714257826272608</v>
       </c>
       <c r="T95">
-        <v>12.78825413587336</v>
+        <v>14.91962982518559</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06578416878788336</v>
+        <v>0.06508433720503355</v>
       </c>
       <c r="W95">
-        <v>0.2202880929998171</v>
+        <v>0.2204531132870531</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2741007032828474</v>
+        <v>0.2711847383543065</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2535114734474655</v>
+        <v>0.2554114734474655</v>
       </c>
       <c r="C96">
-        <v>-1560.558950977106</v>
+        <v>-1590.345995155416</v>
       </c>
       <c r="D96">
-        <v>516.2150490228942</v>
+        <v>511.6490048445836</v>
       </c>
       <c r="E96">
-        <v>1895.474</v>
+        <v>1920.695</v>
       </c>
       <c r="F96">
-        <v>2370.774</v>
+        <v>2395.995</v>
       </c>
       <c r="G96">
         <v>294</v>
@@ -9165,37 +9165,37 @@
         <v>151.6</v>
       </c>
       <c r="M96">
-        <v>559.0285092</v>
+        <v>564.975621</v>
       </c>
       <c r="N96">
-        <v>-407.4285092</v>
+        <v>-413.375621</v>
       </c>
       <c r="O96">
-        <v>-97.78284220800001</v>
+        <v>-99.21014904</v>
       </c>
       <c r="P96">
-        <v>-309.645666992</v>
+        <v>-314.16547196</v>
       </c>
       <c r="Q96">
-        <v>-228.545666992</v>
+        <v>-233.06547196</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7714257826272608</v>
+        <v>0.9165509391527134</v>
       </c>
       <c r="T96">
-        <v>14.91962982518559</v>
+        <v>17.90355579022271</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06508433720503355</v>
+        <v>0.06439923891866477</v>
       </c>
       <c r="W96">
-        <v>0.2204531132870531</v>
+        <v>0.2206146594629789</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2711847383543065</v>
+        <v>0.2683301621611033</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2554114734474655</v>
+        <v>0.2573114734474656</v>
       </c>
       <c r="C97">
-        <v>-1590.345995155416</v>
+        <v>-1620.052972066653</v>
       </c>
       <c r="D97">
-        <v>511.6490048445836</v>
+        <v>507.1630279333472</v>
       </c>
       <c r="E97">
-        <v>1920.695</v>
+        <v>1945.916</v>
       </c>
       <c r="F97">
-        <v>2395.995</v>
+        <v>2421.216</v>
       </c>
       <c r="G97">
         <v>294</v>
@@ -9247,37 +9247,37 @@
         <v>151.6</v>
       </c>
       <c r="M97">
-        <v>564.975621</v>
+        <v>570.9227327999999</v>
       </c>
       <c r="N97">
-        <v>-413.375621</v>
+        <v>-419.3227327999999</v>
       </c>
       <c r="O97">
-        <v>-99.21014904</v>
+        <v>-100.637455872</v>
       </c>
       <c r="P97">
-        <v>-314.16547196</v>
+        <v>-318.685276928</v>
       </c>
       <c r="Q97">
-        <v>-233.06547196</v>
+        <v>-237.585276928</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9165509391527134</v>
+        <v>1.134238673940892</v>
       </c>
       <c r="T97">
-        <v>17.90355579022271</v>
+        <v>22.3794447377784</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06439923891866477</v>
+        <v>0.06372841351326201</v>
       </c>
       <c r="W97">
-        <v>0.2206146594629789</v>
+        <v>0.2207728400935728</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2683301621611033</v>
+        <v>0.2655350563052584</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2573114734474655</v>
+        <v>0.2592114734474655</v>
       </c>
       <c r="C98">
-        <v>-1620.052972066653</v>
+        <v>-1649.681969419985</v>
       </c>
       <c r="D98">
-        <v>507.1630279333472</v>
+        <v>502.7550305800153</v>
       </c>
       <c r="E98">
-        <v>1945.916</v>
+        <v>1971.137</v>
       </c>
       <c r="F98">
-        <v>2421.216</v>
+        <v>2446.437</v>
       </c>
       <c r="G98">
         <v>294</v>
@@ -9329,37 +9329,37 @@
         <v>151.6</v>
       </c>
       <c r="M98">
-        <v>570.9227327999999</v>
+        <v>576.8698446</v>
       </c>
       <c r="N98">
-        <v>-419.3227327999999</v>
+        <v>-425.2698445999999</v>
       </c>
       <c r="O98">
-        <v>-100.637455872</v>
+        <v>-102.064762704</v>
       </c>
       <c r="P98">
-        <v>-318.685276928</v>
+        <v>-323.205081896</v>
       </c>
       <c r="Q98">
-        <v>-237.585276928</v>
+        <v>-242.105081896</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.134238673940889</v>
+        <v>1.497051565254519</v>
       </c>
       <c r="T98">
-        <v>22.37944473777834</v>
+        <v>29.83925965037112</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06372841351326201</v>
+        <v>0.06307141955951705</v>
       </c>
       <c r="W98">
-        <v>0.2207728400935728</v>
+        <v>0.2209277592678659</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2655350563052584</v>
+        <v>0.2627975814979877</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2592114734474655</v>
+        <v>0.2611114734474655</v>
       </c>
       <c r="C99">
-        <v>-1649.681969419985</v>
+        <v>-1679.235002968853</v>
       </c>
       <c r="D99">
-        <v>502.7550305800153</v>
+        <v>498.4229970311467</v>
       </c>
       <c r="E99">
-        <v>1971.137</v>
+        <v>1996.358</v>
       </c>
       <c r="F99">
-        <v>2446.437</v>
+        <v>2471.658</v>
       </c>
       <c r="G99">
         <v>294</v>
@@ -9411,37 +9411,37 @@
         <v>151.6</v>
       </c>
       <c r="M99">
-        <v>576.8698446</v>
+        <v>582.8169564</v>
       </c>
       <c r="N99">
-        <v>-425.2698445999999</v>
+        <v>-431.2169564</v>
       </c>
       <c r="O99">
-        <v>-102.064762704</v>
+        <v>-103.492069536</v>
       </c>
       <c r="P99">
-        <v>-323.205081896</v>
+        <v>-327.724886864</v>
       </c>
       <c r="Q99">
-        <v>-242.105081896</v>
+        <v>-246.624886864</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.497051565254519</v>
+        <v>2.222677347881779</v>
       </c>
       <c r="T99">
-        <v>29.83925965037112</v>
+        <v>44.75888947555668</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06307141955951705</v>
+        <v>0.06242783364564443</v>
       </c>
       <c r="W99">
-        <v>0.2209277592678659</v>
+        <v>0.2210795168263571</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2627975814979877</v>
+        <v>0.2601159735235185</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2611114734474655</v>
+        <v>0.2630114734474655</v>
       </c>
       <c r="C100">
-        <v>-1679.235002968853</v>
+        <v>-1708.714019584552</v>
       </c>
       <c r="D100">
-        <v>498.4229970311467</v>
+        <v>494.164980415448</v>
       </c>
       <c r="E100">
-        <v>1996.358</v>
+        <v>2021.579</v>
       </c>
       <c r="F100">
-        <v>2471.658</v>
+        <v>2496.879</v>
       </c>
       <c r="G100">
         <v>294</v>
@@ -9493,37 +9493,37 @@
         <v>151.6</v>
       </c>
       <c r="M100">
-        <v>582.8169564</v>
+        <v>588.7640682</v>
       </c>
       <c r="N100">
-        <v>-431.2169564</v>
+        <v>-437.1640682</v>
       </c>
       <c r="O100">
-        <v>-103.492069536</v>
+        <v>-104.919376368</v>
       </c>
       <c r="P100">
-        <v>-327.724886864</v>
+        <v>-332.244691832</v>
       </c>
       <c r="Q100">
-        <v>-246.624886864</v>
+        <v>-251.144691832</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.222677347881779</v>
+        <v>4.399554695763557</v>
       </c>
       <c r="T100">
-        <v>44.75888947555668</v>
+        <v>89.51777895111336</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06242783364564443</v>
+        <v>0.06179724946740559</v>
       </c>
       <c r="W100">
-        <v>0.2210795168263571</v>
+        <v>0.2212282085755858</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2601159735235185</v>
+        <v>0.2574885394475234</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2630114734474655</v>
-      </c>
-      <c r="C101">
-        <v>-1708.714019584552</v>
-      </c>
-      <c r="D101">
-        <v>494.164980415448</v>
-      </c>
-      <c r="E101">
-        <v>2021.579</v>
-      </c>
-      <c r="F101">
-        <v>2496.879</v>
-      </c>
-      <c r="G101">
-        <v>294</v>
-      </c>
-      <c r="H101">
-        <v>2046.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>232.7</v>
-      </c>
-      <c r="K101">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>151.6</v>
-      </c>
-      <c r="M101">
-        <v>588.7640682</v>
-      </c>
-      <c r="N101">
-        <v>-437.1640682</v>
-      </c>
-      <c r="O101">
-        <v>-104.919376368</v>
-      </c>
-      <c r="P101">
-        <v>-332.244691832</v>
-      </c>
-      <c r="Q101">
-        <v>-251.144691832</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.399554695763557</v>
-      </c>
-      <c r="T101">
-        <v>89.51777895111336</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06179724946740559</v>
-      </c>
-      <c r="W101">
-        <v>0.2212282085755858</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2574885394475234</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
